--- a/Varify_Product/Product_find.xlsx
+++ b/Varify_Product/Product_find.xlsx
@@ -19,150 +19,423 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="139">
   <si>
     <t>product_code</t>
   </si>
   <si>
-    <t>HSE0210</t>
+    <t>MA0433101</t>
   </si>
   <si>
-    <t>HSE0211</t>
+    <t>FCA0008100</t>
   </si>
   <si>
-    <t>HSE0215</t>
+    <t>ACS0360100</t>
   </si>
   <si>
-    <t>HSE0216</t>
+    <t>LAU021EC071</t>
   </si>
   <si>
-    <t>HSE0218</t>
+    <t>SP0001100</t>
   </si>
   <si>
-    <t>HSE0219</t>
+    <t>ACS004410C</t>
   </si>
   <si>
-    <t>HSE0220</t>
+    <t>SP0035100</t>
   </si>
   <si>
-    <t>HSE0221</t>
+    <t>ACS0021100</t>
   </si>
   <si>
-    <t>HSE0222</t>
+    <t>FCA0001100</t>
   </si>
   <si>
-    <t>HSE0223</t>
+    <t>FCA0006100</t>
   </si>
   <si>
-    <t>HSE0224</t>
+    <t>FU043BQL160</t>
   </si>
   <si>
-    <t>HSE0225</t>
+    <t>LFU43BQL160</t>
   </si>
   <si>
-    <t>HSE0272</t>
+    <t>RS0007101</t>
   </si>
   <si>
-    <t>HSE0273</t>
+    <t>UF0004100</t>
   </si>
   <si>
-    <t>HSE0274</t>
+    <t>MU0001101</t>
   </si>
   <si>
-    <t>HSE0275</t>
+    <t>ACS0031100</t>
   </si>
   <si>
-    <t>HSE0276</t>
+    <t>MLC041101</t>
   </si>
   <si>
-    <t>HSE0278</t>
+    <t>SP0009100</t>
   </si>
   <si>
-    <t>HSE0279</t>
+    <t>MA332B101</t>
   </si>
   <si>
-    <t>HSE0280</t>
+    <t>SP00221100</t>
   </si>
   <si>
-    <t>HSE0281</t>
+    <t>MA0532C110</t>
   </si>
   <si>
-    <t>HSE0282</t>
+    <t>RS00006110</t>
   </si>
   <si>
-    <t>HSE0283</t>
+    <t>FD0008A100</t>
   </si>
   <si>
-    <t>HSE0284</t>
+    <t>SP00223100</t>
   </si>
   <si>
-    <t>HSE0285</t>
+    <t>SP0024100</t>
   </si>
   <si>
-    <t>HSE0256</t>
+    <t>SP00662100</t>
   </si>
   <si>
-    <t>HSE0227</t>
+    <t>WD0001A100</t>
   </si>
   <si>
-    <t>HSE0229</t>
+    <t>FCA0065100</t>
   </si>
   <si>
-    <t>HSE0230</t>
+    <t>MO006901110</t>
   </si>
   <si>
-    <t>HSE0232</t>
+    <t>ACS1360100</t>
   </si>
   <si>
-    <t>HSE0237</t>
+    <t>WB0004A100</t>
   </si>
   <si>
-    <t>HSE0238</t>
+    <t>SP0129100</t>
   </si>
   <si>
-    <t>HSE0239</t>
+    <t>MSP017800</t>
   </si>
   <si>
-    <t>HSE0240</t>
+    <t>MT00211210</t>
   </si>
   <si>
-    <t>HSE0241</t>
+    <t>MT00681110</t>
   </si>
   <si>
-    <t>HSE0242</t>
+    <t>WB0006114</t>
   </si>
   <si>
-    <t>HSE0243</t>
+    <t>FD0012A100</t>
   </si>
   <si>
-    <t>HSE0290</t>
+    <t>SPV002100</t>
   </si>
   <si>
-    <t>HSE0291</t>
+    <t>WB0001A100</t>
   </si>
   <si>
-    <t>HSE0292</t>
+    <t>MO0310101</t>
   </si>
   <si>
-    <t>HSE0293</t>
+    <t>RS00003101</t>
   </si>
   <si>
-    <t>HSE0294</t>
+    <t>MA0048101</t>
   </si>
   <si>
-    <t>HSE0298</t>
+    <t>MO0025101</t>
   </si>
   <si>
-    <t>HSE0299</t>
+    <t>MU0002101</t>
   </si>
   <si>
-    <t>HSE0302</t>
+    <t>SPV0005100</t>
   </si>
   <si>
-    <t>HSE0303</t>
+    <t>SPV0017100</t>
   </si>
   <si>
-    <t>HSE0304</t>
+    <t>SP00212100</t>
+  </si>
+  <si>
+    <t>MF0025163</t>
+  </si>
+  <si>
+    <t>MO0010101</t>
+  </si>
+  <si>
+    <t>MSW0004101.</t>
+  </si>
+  <si>
+    <t>MA0523C110</t>
+  </si>
+  <si>
+    <t>MA575C110</t>
+  </si>
+  <si>
+    <t>FCA0015100</t>
+  </si>
+  <si>
+    <t>SPV004100</t>
+  </si>
+  <si>
+    <t>RS00005110</t>
+  </si>
+  <si>
+    <t>FCA0096100</t>
+  </si>
+  <si>
+    <t>FCA0083101</t>
+  </si>
+  <si>
+    <t>FCS0004100</t>
+  </si>
+  <si>
+    <t>FCA0077101</t>
+  </si>
+  <si>
+    <t>MUS008100</t>
+  </si>
+  <si>
+    <t>SWR0004100</t>
+  </si>
+  <si>
+    <t>FP0500D7L97A</t>
+  </si>
+  <si>
+    <t>ERS0026110</t>
+  </si>
+  <si>
+    <t>SP0025100</t>
+  </si>
+  <si>
+    <t>F043E5C022</t>
+  </si>
+  <si>
+    <t>MO00691110</t>
+  </si>
+  <si>
+    <t>MW0003101</t>
+  </si>
+  <si>
+    <t>MA0241101</t>
+  </si>
+  <si>
+    <t>MT00431210</t>
+  </si>
+  <si>
+    <t>MA0035101</t>
+  </si>
+  <si>
+    <t>RS0008102</t>
+  </si>
+  <si>
+    <t>SWH006100</t>
+  </si>
+  <si>
+    <t>MA0174101</t>
+  </si>
+  <si>
+    <t>MG005110A</t>
+  </si>
+  <si>
+    <t>MG005210A</t>
+  </si>
+  <si>
+    <t>MAC0001B0010000</t>
+  </si>
+  <si>
+    <t>MAE071R110</t>
+  </si>
+  <si>
+    <t>HSW0001100</t>
+  </si>
+  <si>
+    <t>MA0154101</t>
+  </si>
+  <si>
+    <t>MO010S101</t>
+  </si>
+  <si>
+    <t>AC0062101</t>
+  </si>
+  <si>
+    <t>ACS2360100</t>
+  </si>
+  <si>
+    <t>MO00521210</t>
+  </si>
+  <si>
+    <t>MO25SU10</t>
+  </si>
+  <si>
+    <t>SP00388/4</t>
+  </si>
+  <si>
+    <t>MO0026101A</t>
+  </si>
+  <si>
+    <t>SP00283101</t>
+  </si>
+  <si>
+    <t>MT014B101</t>
+  </si>
+  <si>
+    <t>SPH101100</t>
+  </si>
+  <si>
+    <t>MO261S101</t>
+  </si>
+  <si>
+    <t>SP00204100</t>
+  </si>
+  <si>
+    <t>MO511S101</t>
+  </si>
+  <si>
+    <t>SPH0051100</t>
+  </si>
+  <si>
+    <t>SP00283100</t>
+  </si>
+  <si>
+    <t>SP0008100</t>
+  </si>
+  <si>
+    <t>SP00452101</t>
+  </si>
+  <si>
+    <t>SPW0069100</t>
+  </si>
+  <si>
+    <t>SPW074003</t>
+  </si>
+  <si>
+    <t>SWH0002100</t>
+  </si>
+  <si>
+    <t>MT41TC101</t>
+  </si>
+  <si>
+    <t>MO049EXC101</t>
+  </si>
+  <si>
+    <t>MAL110C1010</t>
+  </si>
+  <si>
+    <t>MO079S101</t>
+  </si>
+  <si>
+    <t>SPH040100</t>
+  </si>
+  <si>
+    <t>SP00282100</t>
+  </si>
+  <si>
+    <t>SP0404101</t>
+  </si>
+  <si>
+    <t>MA212B101</t>
+  </si>
+  <si>
+    <t>NFG03-143SPC12001400-IDO</t>
+  </si>
+  <si>
+    <t>SPW0069300</t>
+  </si>
+  <si>
+    <t>SPU016100</t>
+  </si>
+  <si>
+    <t>SPH0068110</t>
+  </si>
+  <si>
+    <t>MT14TC101</t>
+  </si>
+  <si>
+    <t>NFG03-NT-12001200E-5802L</t>
+  </si>
+  <si>
+    <t>NFG03-NT-12001200F-5802L</t>
+  </si>
+  <si>
+    <t>SWH483H100</t>
+  </si>
+  <si>
+    <t>SPU011100</t>
+  </si>
+  <si>
+    <t>NFG02-32-095-A-5802-L</t>
+  </si>
+  <si>
+    <t>SPH066100</t>
+  </si>
+  <si>
+    <t>SPH079100</t>
+  </si>
+  <si>
+    <t>NRSF8-801-C001-0046</t>
+  </si>
+  <si>
+    <t>NRSF8-803-0002-083</t>
+  </si>
+  <si>
+    <t>NFG03-NT-5301650-5802</t>
+  </si>
+  <si>
+    <t>RS00006100</t>
+  </si>
+  <si>
+    <t>NFG03-NT-2501200-5802</t>
+  </si>
+  <si>
+    <t>SWH0003100</t>
+  </si>
+  <si>
+    <t>SPU003100</t>
+  </si>
+  <si>
+    <t>SPU007100</t>
+  </si>
+  <si>
+    <t>MO049EX101</t>
+  </si>
+  <si>
+    <t>NFG03-SPC-1501150-8019</t>
+  </si>
+  <si>
+    <t>NFG03-SPC-2751150-8019</t>
+  </si>
+  <si>
+    <t>NFG03-SPC-15001400-8019</t>
+  </si>
+  <si>
+    <t>NFG05-GL-332-681</t>
+  </si>
+  <si>
+    <t>NFG05-GL-603-650</t>
+  </si>
+  <si>
+    <t>NFG05-GL-564-642</t>
+  </si>
+  <si>
+    <t>NFG05-GL-622-650</t>
+  </si>
+  <si>
+    <t>NFG05-GL-604-681</t>
+  </si>
+  <si>
+    <t>NFG03-NT-1821500-5802</t>
+  </si>
+  <si>
+    <t>NFG03-NT-12001200-5802</t>
   </si>
 </sst>
 </file>
@@ -182,16 +455,19 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Angsana New"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="18"/>
       <color indexed="8"/>
       <name val="Angsana New"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Angsana New"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="16"/>
@@ -1600,7 +1876,7 @@
     </row>
     <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1609,7 +1885,7 @@
     </row>
     <row r="15" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
@@ -1618,7 +1894,7 @@
     </row>
     <row r="16" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
@@ -1627,7 +1903,7 @@
     </row>
     <row r="17" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
@@ -1636,7 +1912,7 @@
     </row>
     <row r="18" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
@@ -1645,7 +1921,7 @@
     </row>
     <row r="19" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
@@ -1654,7 +1930,7 @@
     </row>
     <row r="20" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
@@ -1663,7 +1939,7 @@
     </row>
     <row r="21" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
@@ -1672,7 +1948,7 @@
     </row>
     <row r="22" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
@@ -1681,7 +1957,7 @@
     </row>
     <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
@@ -1690,7 +1966,7 @@
     </row>
     <row r="24" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -1699,7 +1975,7 @@
     </row>
     <row r="25" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
@@ -1708,7 +1984,7 @@
     </row>
     <row r="26" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
@@ -1717,7 +1993,7 @@
     </row>
     <row r="27" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
@@ -1726,7 +2002,7 @@
     </row>
     <row r="28" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1735,7 +2011,7 @@
     </row>
     <row r="29" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="3"/>
@@ -1744,7 +2020,7 @@
     </row>
     <row r="30" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="3"/>
@@ -1753,7 +2029,7 @@
     </row>
     <row r="31" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="3"/>
@@ -1762,7 +2038,7 @@
     </row>
     <row r="32" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
@@ -1771,7 +2047,7 @@
     </row>
     <row r="33" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="3"/>
@@ -1780,7 +2056,7 @@
     </row>
     <row r="34" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
@@ -1789,7 +2065,7 @@
     </row>
     <row r="35" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="3"/>
@@ -1798,7 +2074,7 @@
     </row>
     <row r="36" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="3"/>
@@ -1807,7 +2083,7 @@
     </row>
     <row r="37" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="3"/>
@@ -1816,7 +2092,7 @@
     </row>
     <row r="38" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -1825,7 +2101,7 @@
     </row>
     <row r="39" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="3"/>
@@ -1834,7 +2110,7 @@
     </row>
     <row r="40" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="3"/>
@@ -1843,7 +2119,7 @@
     </row>
     <row r="41" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="3"/>
@@ -1852,7 +2128,7 @@
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1861,7 +2137,7 @@
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="3"/>
@@ -1870,7 +2146,7 @@
     </row>
     <row r="44" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="3"/>
@@ -1879,7 +2155,7 @@
     </row>
     <row r="45" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="3"/>
@@ -1888,7 +2164,7 @@
     </row>
     <row r="46" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="3"/>
@@ -1897,7 +2173,7 @@
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="3"/>
@@ -1906,7 +2182,7 @@
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
@@ -1914,1043 +2190,1341 @@
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
+      <c r="A49" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="B49" s="2"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5"/>
+      <c r="A50" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="B50" s="2"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
+      <c r="A51" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B51" s="2"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
+      <c r="A52" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="B52" s="2"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
+      <c r="A53" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="B53" s="2"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5"/>
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="B54" s="2"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="B55" s="2"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
+      <c r="A56" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5"/>
+      <c r="A57" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="B57" s="2"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5"/>
+      <c r="A58" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="B58" s="2"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
+      <c r="A59" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="B59" s="2"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
+      <c r="A60" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="B60" s="2"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5"/>
+      <c r="A61" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B61" s="2"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5"/>
+      <c r="A62" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="B62" s="2"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
+      <c r="A63" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="B63" s="2"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5"/>
+      <c r="A64" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="B64" s="2"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5"/>
+      <c r="A65" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
+      <c r="A66" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="B66" s="2"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5"/>
+      <c r="A67" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="B67" s="2"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
+      <c r="A68" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="B68" s="2"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5"/>
+      <c r="A69" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5"/>
+      <c r="A70" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="B70" s="2"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
+      <c r="A71" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="B71" s="2"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
     <row r="72" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5"/>
+      <c r="A72" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="B72" s="2"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5"/>
+      <c r="A73" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="B73" s="2"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5"/>
+      <c r="A74" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="B74" s="2"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
+      <c r="A75" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="B75" s="2"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5"/>
+      <c r="A76" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="B76" s="2"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="5"/>
+      <c r="A77" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="B77" s="2"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="5"/>
+      <c r="A78" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5"/>
+      <c r="A79" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5"/>
+      <c r="A80" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5"/>
+      <c r="A81" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5"/>
+      <c r="A82" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5"/>
+      <c r="A83" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5"/>
+      <c r="A84" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="5"/>
+      <c r="A85" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="B85" s="2"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5"/>
+      <c r="A86" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5"/>
+      <c r="A87" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="B87" s="2"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5"/>
+      <c r="A88" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B88" s="2"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5"/>
+      <c r="A89" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5"/>
+      <c r="A90" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5"/>
+      <c r="A91" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5"/>
+      <c r="A92" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5"/>
+      <c r="A93" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="5"/>
+      <c r="A94" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5"/>
+      <c r="A95" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5"/>
+      <c r="A96" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="5"/>
+      <c r="A97" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5"/>
+      <c r="A98" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="B98" s="2"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5"/>
+      <c r="A99" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="B99" s="2"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5"/>
+      <c r="A100" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="B100" s="2"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5"/>
+      <c r="A101" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="B101" s="2"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
+      <c r="A102" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="B102" s="2"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
+      <c r="A103" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
+      <c r="A104" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="B104" s="2"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="5"/>
+      <c r="A105" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="B105" s="2"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="5"/>
+      <c r="A106" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="B106" s="2"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
+      <c r="A107" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="B107" s="2"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5"/>
+      <c r="A108" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="B108" s="2"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="5"/>
+      <c r="A109" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="B109" s="2"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="5"/>
+      <c r="A110" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="B110" s="2"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
+      <c r="A111" s="5" t="s">
+        <v>74</v>
+      </c>
       <c r="B111" s="2"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
+      <c r="A112" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="B112" s="2"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="5"/>
+      <c r="A113" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5"/>
+      <c r="A114" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="B114" s="2"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
+      <c r="A115" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="B115" s="2"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
+      <c r="A116" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="B116" s="2"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="5"/>
+      <c r="A117" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="B117" s="2"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="5"/>
+      <c r="A118" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="B118" s="2"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
+      <c r="A119" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="B119" s="2"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
     <row r="120" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
+      <c r="A120" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="B120" s="2"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
     <row r="121" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
+      <c r="A121" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="B121" s="2"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
     <row r="122" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="5"/>
+      <c r="A122" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="B122" s="2"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
+      <c r="A123" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="B123" s="2"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
+      <c r="A124" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="B124" s="2"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="5"/>
+      <c r="A125" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="B125" s="2"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="5"/>
+      <c r="A126" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="B126" s="2"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
+      <c r="A127" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="B127" s="2"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
+      <c r="A128" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="B128" s="2"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
     <row r="129" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="5"/>
+      <c r="A129" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="B129" s="2"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
     <row r="130" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="5"/>
+      <c r="A130" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
     <row r="131" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
+      <c r="A131" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
+      <c r="A132" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
     <row r="133" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="5"/>
+      <c r="A133" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
     <row r="134" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="5"/>
+      <c r="A134" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="B134" s="2"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
     <row r="135" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
+      <c r="A135" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="B135" s="2"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
     <row r="136" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
+      <c r="A136" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="B136" s="2"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
     <row r="137" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="5"/>
+      <c r="A137" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="B137" s="2"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
     <row r="138" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="5"/>
+      <c r="A138" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="B138" s="2"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
     <row r="139" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
+      <c r="A139" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="B139" s="2"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
     <row r="140" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
+      <c r="A140" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="B140" s="2"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
     <row r="141" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="5"/>
+      <c r="A141" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="B141" s="2"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
     </row>
     <row r="142" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="5"/>
+      <c r="A142" s="5" t="s">
+        <v>97</v>
+      </c>
       <c r="B142" s="2"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
     </row>
     <row r="143" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
+      <c r="A143" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="B143" s="2"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
     </row>
     <row r="144" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
+      <c r="A144" s="5" t="s">
+        <v>99</v>
+      </c>
       <c r="B144" s="2"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
     </row>
     <row r="145" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="5"/>
+      <c r="A145" s="5" t="s">
+        <v>100</v>
+      </c>
       <c r="B145" s="2"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
     </row>
     <row r="146" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="5"/>
+      <c r="A146" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="B146" s="2"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="5"/>
+      <c r="A147" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="B147" s="2"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="5"/>
+      <c r="A148" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="B148" s="2"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="5"/>
+      <c r="A149" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="B149" s="2"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="5"/>
+      <c r="A150" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="B150" s="2"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="5"/>
+      <c r="A151" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="B151" s="2"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="5"/>
+      <c r="A152" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="B152" s="2"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="5"/>
+      <c r="A153" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="B153" s="2"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="5"/>
+      <c r="A154" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="B154" s="2"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
     <row r="155" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="5"/>
+      <c r="A155" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="B155" s="2"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
     </row>
     <row r="156" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="5"/>
+      <c r="A156" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="B156" s="2"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="5"/>
+      <c r="A157" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="B157" s="2"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
     </row>
     <row r="158" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="5"/>
+      <c r="A158" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="B158" s="2"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
     <row r="159" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="5"/>
+      <c r="A159" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="B159" s="2"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
     </row>
     <row r="160" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="5"/>
+      <c r="A160" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
     <row r="161" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="5"/>
+      <c r="A161" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="B161" s="2"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
     </row>
     <row r="162" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="5"/>
+      <c r="A162" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="B162" s="2"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
     </row>
     <row r="163" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="5"/>
+      <c r="A163" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="B163" s="2"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
     </row>
     <row r="164" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="5"/>
+      <c r="A164" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="B164" s="2"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
     <row r="165" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="5"/>
+      <c r="A165" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="B165" s="2"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
     </row>
     <row r="166" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="5"/>
+      <c r="A166" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="B166" s="2"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
     <row r="167" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="5"/>
+      <c r="A167" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="B167" s="2"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
     </row>
     <row r="168" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="5"/>
+      <c r="A168" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="B168" s="2"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
     </row>
     <row r="169" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="5"/>
+      <c r="A169" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="B169" s="2"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
     </row>
     <row r="170" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="5"/>
+      <c r="A170" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="B170" s="2"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
     <row r="171" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="5"/>
+      <c r="A171" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="B171" s="2"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
     </row>
     <row r="172" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="5"/>
+      <c r="A172" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="B172" s="2"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
     <row r="173" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="5"/>
+      <c r="A173" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="B173" s="2"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
     </row>
     <row r="174" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="5"/>
+      <c r="A174" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="B174" s="2"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
     </row>
     <row r="175" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="5"/>
+      <c r="A175" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="B175" s="2"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
     </row>
     <row r="176" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="5"/>
+      <c r="A176" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="B176" s="2"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
     </row>
     <row r="177" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="5"/>
+      <c r="A177" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="B177" s="2"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
     </row>
     <row r="178" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A178" s="6"/>
+      <c r="A178" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="B178" s="2"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
     </row>
     <row r="179" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A179" s="6"/>
+      <c r="A179" s="6" t="s">
+        <v>123</v>
+      </c>
       <c r="B179" s="2"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
     </row>
     <row r="180" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A180" s="6"/>
+      <c r="A180" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="B180" s="2"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
     </row>
     <row r="181" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A181" s="6"/>
+      <c r="A181" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="B181" s="2"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
     </row>
     <row r="182" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A182" s="6"/>
+      <c r="A182" s="6" t="s">
+        <v>125</v>
+      </c>
       <c r="B182" s="2"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
     </row>
     <row r="183" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A183" s="6"/>
+      <c r="A183" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="B183" s="2"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
     </row>
     <row r="184" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A184" s="6"/>
+      <c r="A184" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="B184" s="2"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
     </row>
     <row r="185" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A185" s="6"/>
+      <c r="A185" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="B185" s="2"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
     </row>
     <row r="186" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A186" s="6"/>
+      <c r="A186" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="B186" s="2"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
     </row>
     <row r="187" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A187" s="6"/>
+      <c r="A187" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
     </row>
     <row r="188" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A188" s="6"/>
+      <c r="A188" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="B188" s="2"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
     </row>
     <row r="189" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A189" s="6"/>
+      <c r="A189" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="B189" s="2"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
     </row>
     <row r="190" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A190" s="6"/>
+      <c r="A190" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="B190" s="2"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
     </row>
     <row r="191" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A191" s="6"/>
+      <c r="A191" s="6" t="s">
+        <v>132</v>
+      </c>
       <c r="B191" s="2"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
     </row>
     <row r="192" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A192" s="6"/>
+      <c r="A192" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="B192" s="2"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
     </row>
     <row r="193" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A193" s="6"/>
+      <c r="A193" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="B193" s="2"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
     </row>
     <row r="194" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A194" s="6"/>
+      <c r="A194" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="B194" s="2"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
     <row r="195" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A195" s="6"/>
+      <c r="A195" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="B195" s="2"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
     </row>
     <row r="196" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A196" s="6"/>
+      <c r="A196" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="B196" s="2"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
     <row r="197" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A197" s="6"/>
+      <c r="A197" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B197" s="2"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>

--- a/Varify_Product/Product_find.xlsx
+++ b/Varify_Product/Product_find.xlsx
@@ -11,693 +11,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>product_code</t>
   </si>
   <si>
-    <t>MF015N153</t>
+    <t>SP00010101</t>
   </si>
   <si>
-    <t>MO00381211</t>
+    <t>SP00273100</t>
   </si>
   <si>
-    <t>MO0830ADC10000</t>
+    <t>SPF0001200</t>
   </si>
   <si>
-    <t>LAM0056DGC12115</t>
+    <t>SPF0003200</t>
   </si>
   <si>
-    <t>ERS0033100</t>
+    <t>SPF0004200</t>
   </si>
   <si>
-    <t>MT20SS101</t>
+    <t>FCA0006100</t>
   </si>
   <si>
-    <t>SSPW013100</t>
-  </si>
-  <si>
-    <t>MSR100F0C10000</t>
-  </si>
-  <si>
-    <t>FU00050DDL1303</t>
-  </si>
-  <si>
-    <t>FU00025DFC11514</t>
-  </si>
-  <si>
-    <t>MT00003I0010000</t>
-  </si>
-  <si>
-    <t>MT21NS1101</t>
-  </si>
-  <si>
-    <t>MT341S101</t>
-  </si>
-  <si>
-    <t>MA0422101</t>
-  </si>
-  <si>
-    <t>MA0433101</t>
-  </si>
-  <si>
-    <t>MO049EX1210</t>
-  </si>
-  <si>
-    <t>FM0500D7L98A</t>
-  </si>
-  <si>
-    <t>FM0500D7L99A</t>
-  </si>
-  <si>
-    <t>MA0651C110</t>
-  </si>
-  <si>
-    <t>FU00050DDL11521</t>
-  </si>
-  <si>
-    <t>MO00521210</t>
-  </si>
-  <si>
-    <t>FO0020G5C75</t>
-  </si>
-  <si>
-    <t>SPW02N2110</t>
-  </si>
-  <si>
-    <t>MO12SP1210</t>
-  </si>
-  <si>
-    <t>MA172B101</t>
-  </si>
-  <si>
-    <t>LA0213262</t>
-  </si>
-  <si>
-    <t>MT0033S110</t>
-  </si>
-  <si>
-    <t>MUS008100</t>
-  </si>
-  <si>
-    <t>MU00071010</t>
-  </si>
-  <si>
-    <t>MO00691110</t>
-  </si>
-  <si>
-    <t>FCS0005100</t>
-  </si>
-  <si>
-    <t>SP0025100</t>
-  </si>
-  <si>
-    <t>FDP0008A100</t>
-  </si>
-  <si>
-    <t>RS00003101</t>
-  </si>
-  <si>
-    <t>MO0026101</t>
-  </si>
-  <si>
-    <t>AC0051101</t>
+    <t>SP0001100</t>
   </si>
   <si>
     <t>SP0003100</t>
   </si>
   <si>
-    <t>MM01SP100</t>
+    <t>SP0008100</t>
   </si>
   <si>
-    <t>MO010S101</t>
+    <t>SP0033100</t>
   </si>
   <si>
-    <t>MF015N152</t>
+    <t>SP0039100</t>
   </si>
   <si>
-    <t>MO261S101</t>
+    <t>SP0040100</t>
   </si>
   <si>
-    <t>MOS066100</t>
-  </si>
-  <si>
-    <t>MO049EX101</t>
-  </si>
-  <si>
-    <t>FM0034D5C970</t>
-  </si>
-  <si>
-    <t>FM0500D7R99A</t>
-  </si>
-  <si>
-    <t>SWH006100</t>
-  </si>
-  <si>
-    <t>FU00650G107</t>
-  </si>
-  <si>
-    <t>MO0661013</t>
-  </si>
-  <si>
-    <t>LAM017QL1420</t>
-  </si>
-  <si>
-    <t>LAM017QR1420</t>
-  </si>
-  <si>
-    <t>MSW0012103</t>
-  </si>
-  <si>
-    <t>FU0025HC19</t>
-  </si>
-  <si>
-    <t>MAE06DL101</t>
-  </si>
-  <si>
-    <t>MO00501210</t>
-  </si>
-  <si>
-    <t>FU043AQC160</t>
-  </si>
-  <si>
-    <t>MT00431210</t>
-  </si>
-  <si>
-    <t>MT00441210</t>
-  </si>
-  <si>
-    <t>MO00421210</t>
-  </si>
-  <si>
-    <t>FCA0006100</t>
-  </si>
-  <si>
-    <t>MT00411210</t>
-  </si>
-  <si>
-    <t>SP00212100</t>
-  </si>
-  <si>
-    <t>MO040S101</t>
-  </si>
-  <si>
-    <t>MT411S101</t>
-  </si>
-  <si>
-    <t>SP0001100</t>
-  </si>
-  <si>
-    <t>MAE011101</t>
-  </si>
-  <si>
-    <t>MO006901110</t>
-  </si>
-  <si>
-    <t>MO050H0C10000</t>
-  </si>
-  <si>
-    <t>NXMAE011101</t>
-  </si>
-  <si>
-    <t>F00530F03002</t>
-  </si>
-  <si>
-    <t>FU00640300</t>
-  </si>
-  <si>
-    <t>MA702B101</t>
-  </si>
-  <si>
-    <t>MA702P101</t>
-  </si>
-  <si>
-    <t>FU00043DEC21511</t>
-  </si>
-  <si>
-    <t>NX0702BB0010000</t>
-  </si>
-  <si>
-    <t>NX0702PB0010000</t>
-  </si>
-  <si>
-    <t>FA0080C5R03</t>
-  </si>
-  <si>
-    <t>FCF0002100</t>
-  </si>
-  <si>
-    <t>AC0061101</t>
-  </si>
-  <si>
-    <t>MO002S101</t>
-  </si>
-  <si>
-    <t>SPW011100</t>
-  </si>
-  <si>
-    <t>MA183A101</t>
-  </si>
-  <si>
-    <t>SPW16N410</t>
-  </si>
-  <si>
-    <t>MO0310101</t>
-  </si>
-  <si>
-    <t>MO005N101.</t>
-  </si>
-  <si>
-    <t>VT00433101</t>
-  </si>
-  <si>
-    <t>MO0050EX1210</t>
-  </si>
-  <si>
-    <t>MUS010100</t>
-  </si>
-  <si>
-    <t>SPH0050000</t>
-  </si>
-  <si>
-    <t>MO0050101A</t>
-  </si>
-  <si>
-    <t>SPW0403100</t>
-  </si>
-  <si>
-    <t>SPW20N2110</t>
-  </si>
-  <si>
-    <t>MO00661210</t>
-  </si>
-  <si>
-    <t>MA0154101</t>
-  </si>
-  <si>
-    <t>MA0212201.</t>
-  </si>
-  <si>
-    <t>MA322B101</t>
-  </si>
-  <si>
-    <t>MT14TC101</t>
-  </si>
-  <si>
-    <t>SPW41N1100</t>
-  </si>
-  <si>
-    <t>FU0033FC1560</t>
-  </si>
-  <si>
-    <t>FU0065G1L180</t>
-  </si>
-  <si>
-    <t>FM057G2C212L</t>
-  </si>
-  <si>
-    <t>FM0570JC212</t>
-  </si>
-  <si>
-    <t>FM057HC212</t>
-  </si>
-  <si>
-    <t>FM00057DN911912</t>
-  </si>
-  <si>
-    <t>SWR0001100</t>
-  </si>
-  <si>
-    <t>ERS0001115</t>
-  </si>
-  <si>
-    <t>MSH0012303.</t>
-  </si>
-  <si>
-    <t>MA0475C110</t>
-  </si>
-  <si>
-    <t>MA332B1101</t>
-  </si>
-  <si>
-    <t>SWR0007100</t>
-  </si>
-  <si>
-    <t>LAM011KC157218</t>
-  </si>
-  <si>
-    <t>FAU080C5R02</t>
-  </si>
-  <si>
-    <t>SPW264100</t>
+    <t>SP0103100</t>
   </si>
   <si>
     <t>SPO001100</t>
   </si>
   <si>
-    <t>MW0002101</t>
+    <t>SPV002100</t>
   </si>
   <si>
-    <t>SP0035100</t>
+    <t>SPV003100</t>
   </si>
   <si>
-    <t>SPW143N10</t>
+    <t>SPW005N110</t>
   </si>
   <si>
-    <t>MA0174101</t>
+    <t>SPW012100</t>
   </si>
   <si>
-    <t>SPU011100</t>
+    <t>SPW026100</t>
   </si>
   <si>
-    <t>MTK00031112</t>
+    <t>SPW19N100</t>
   </si>
   <si>
-    <t>SPW41N3100</t>
+    <t>WB0005A100</t>
   </si>
   <si>
-    <t>SPW0791100</t>
-  </si>
-  <si>
-    <t>MSW0015100</t>
-  </si>
-  <si>
-    <t>FCA0096SP100</t>
-  </si>
-  <si>
-    <t>MT055E1210</t>
-  </si>
-  <si>
-    <t>ERS0029100</t>
-  </si>
-  <si>
-    <t>MA0241101</t>
-  </si>
-  <si>
-    <t>FCA0096100</t>
-  </si>
-  <si>
-    <t>MO00001A0S10000</t>
-  </si>
-  <si>
-    <t>MO00002A0S10000</t>
-  </si>
-  <si>
-    <t>MA00028B0010000</t>
-  </si>
-  <si>
-    <t>FCA0003100</t>
-  </si>
-  <si>
-    <t>SPW074002</t>
-  </si>
-  <si>
-    <t>SPW074001</t>
-  </si>
-  <si>
-    <t>FU0025IRL180</t>
-  </si>
-  <si>
-    <t>FU0050E3L1730</t>
-  </si>
-  <si>
-    <t>MO0079S0111</t>
-  </si>
-  <si>
-    <t>MO0870NDC10000</t>
-  </si>
-  <si>
-    <t>FU00053DFC21521</t>
-  </si>
-  <si>
-    <t>LAM0054DGC12115</t>
-  </si>
-  <si>
-    <t>MO00050A0010000</t>
-  </si>
-  <si>
-    <t>MT0081SA0010000</t>
-  </si>
-  <si>
-    <t>MO0830SADC10000</t>
-  </si>
-  <si>
-    <t>LAM0039DKC12115</t>
-  </si>
-  <si>
-    <t>FU0025IR180</t>
-  </si>
-  <si>
-    <t>MA0532C110</t>
-  </si>
-  <si>
-    <t>AC0052101</t>
-  </si>
-  <si>
-    <t>SPW032100</t>
-  </si>
-  <si>
-    <t>SPW034100</t>
-  </si>
-  <si>
-    <t>SPW16N100</t>
-  </si>
-  <si>
-    <t>MA0302201</t>
-  </si>
-  <si>
-    <t>MBT04400</t>
-  </si>
-  <si>
-    <t>ACL0001110</t>
-  </si>
-  <si>
-    <t>SPW0263100</t>
-  </si>
-  <si>
-    <t>NX00651C110</t>
-  </si>
-  <si>
-    <t>MO0880NCC10000</t>
-  </si>
-  <si>
-    <t>MAE06DR101</t>
-  </si>
-  <si>
-    <t>MB025P101.</t>
-  </si>
-  <si>
-    <t>NX000532C110</t>
-  </si>
-  <si>
-    <t>SP00132100.</t>
-  </si>
-  <si>
-    <t>MAL08NIC00</t>
-  </si>
-  <si>
-    <t>AC0013100</t>
-  </si>
-  <si>
-    <t>SPW0264100</t>
-  </si>
-  <si>
-    <t>FU0050C8R55</t>
-  </si>
-  <si>
-    <t>FM0540HC2050</t>
-  </si>
-  <si>
-    <t>NX4FU0050C8R55</t>
-  </si>
-  <si>
-    <t>FM0520K4L5060</t>
-  </si>
-  <si>
-    <t>FM0520K4R5060</t>
-  </si>
-  <si>
-    <t>SP00028D0012017</t>
-  </si>
-  <si>
-    <t>MT00561018</t>
-  </si>
-  <si>
-    <t>F043E5C022</t>
-  </si>
-  <si>
-    <t>MA0054101</t>
-  </si>
-  <si>
-    <t>MA0142101</t>
-  </si>
-  <si>
-    <t>MA142B101</t>
-  </si>
-  <si>
-    <t>MA142P101</t>
-  </si>
-  <si>
-    <t>MA0094201</t>
-  </si>
-  <si>
-    <t>MA0603F12</t>
-  </si>
-  <si>
-    <t>NX5MSW0009101</t>
-  </si>
-  <si>
-    <t>NX5ACS0042100</t>
-  </si>
-  <si>
-    <t>FM0025HC1250</t>
-  </si>
-  <si>
-    <t>MO00771310</t>
-  </si>
-  <si>
-    <t>NX5WB0008110</t>
-  </si>
-  <si>
-    <t>MSW0013101</t>
-  </si>
-  <si>
-    <t>NX5ACA041100</t>
-  </si>
-  <si>
-    <t>FU00001DGL11816</t>
-  </si>
-  <si>
-    <t>FU00002DGR11816</t>
-  </si>
-  <si>
-    <t>FU00003DFC11816</t>
-  </si>
-  <si>
-    <t>LAU020FC03</t>
-  </si>
-  <si>
-    <t>NX5ACS44L100</t>
-  </si>
-  <si>
-    <t>FU0056JC180</t>
-  </si>
-  <si>
-    <t>NX5FU053HC51</t>
-  </si>
-  <si>
-    <t>NX5SPV007100</t>
-  </si>
-  <si>
-    <t>NX5AC001100</t>
-  </si>
-  <si>
-    <t>NX5AC0002100</t>
-  </si>
-  <si>
-    <t>NX5AC0003100</t>
-  </si>
-  <si>
-    <t>NX043E5C021</t>
-  </si>
-  <si>
-    <t>NX5AC0023100</t>
-  </si>
-  <si>
-    <t>NX5AC0033100</t>
-  </si>
-  <si>
-    <t>NX4FU043BQL161</t>
-  </si>
-  <si>
-    <t>NXMI240100</t>
-  </si>
-  <si>
-    <t>NXMI140100</t>
-  </si>
-  <si>
-    <t>NXSP024100</t>
-  </si>
-  <si>
-    <t>NXSP204100</t>
-  </si>
-  <si>
-    <t>NX4FU043AQC160</t>
-  </si>
-  <si>
-    <t>NXF0105DC021</t>
-  </si>
-  <si>
-    <t>NX4LAU021EC071</t>
-  </si>
-  <si>
-    <t>NX5ACA0415100</t>
-  </si>
-  <si>
-    <t>NX5FCF0002100</t>
-  </si>
-  <si>
-    <t>NX4FU042D3C55</t>
-  </si>
-  <si>
-    <t>NX5SWR0001100</t>
-  </si>
-  <si>
-    <t>NX5AC0014100</t>
-  </si>
-  <si>
-    <t>MA0523C110</t>
-  </si>
-  <si>
-    <t>ACS0021100</t>
-  </si>
-  <si>
-    <t>MF025L123</t>
-  </si>
-  <si>
-    <t>MO031N1310</t>
-  </si>
-  <si>
-    <t>3FA0040JR03B</t>
-  </si>
-  <si>
-    <t>WD0001SP100</t>
-  </si>
-  <si>
-    <t>ACL0002111</t>
-  </si>
-  <si>
-    <t>FU0050C8R179</t>
-  </si>
-  <si>
-    <t>SPH0068110</t>
-  </si>
-  <si>
-    <t>FCA0009100</t>
-  </si>
-  <si>
-    <t>MAE013C110</t>
-  </si>
-  <si>
-    <t>SPW0422100</t>
-  </si>
-  <si>
-    <t>MW004S101</t>
-  </si>
-  <si>
-    <t>MO031N101</t>
-  </si>
-  <si>
-    <t>MO032S101</t>
-  </si>
-  <si>
-    <t>MO0850NDC10000</t>
-  </si>
-  <si>
-    <t>ERS0006110</t>
-  </si>
-  <si>
-    <t>MO0069S1101</t>
+    <t>WD0003100</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +1507,7 @@
     </row>
     <row r="9" ht="13.5" customHeight="1">
       <c r="A9" t="s" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
@@ -2134,7 +1516,7 @@
     </row>
     <row r="10" ht="13.5" customHeight="1">
       <c r="A10" t="s" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
@@ -2143,7 +1525,7 @@
     </row>
     <row r="11" ht="13.5" customHeight="1">
       <c r="A11" t="s" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
@@ -2152,7 +1534,7 @@
     </row>
     <row r="12" ht="13.5" customHeight="1">
       <c r="A12" t="s" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
@@ -2161,7 +1543,7 @@
     </row>
     <row r="13" ht="13.5" customHeight="1">
       <c r="A13" t="s" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
@@ -2170,7 +1552,7 @@
     </row>
     <row r="14" ht="13.5" customHeight="1">
       <c r="A14" t="s" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4"/>
@@ -2179,7 +1561,7 @@
     </row>
     <row r="15" ht="13.5" customHeight="1">
       <c r="A15" t="s" s="6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
@@ -2188,7 +1570,7 @@
     </row>
     <row r="16" ht="13.5" customHeight="1">
       <c r="A16" t="s" s="6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
@@ -2197,7 +1579,7 @@
     </row>
     <row r="17" ht="13.5" customHeight="1">
       <c r="A17" t="s" s="6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
@@ -2206,7 +1588,7 @@
     </row>
     <row r="18" ht="13.5" customHeight="1">
       <c r="A18" t="s" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
@@ -2215,7 +1597,7 @@
     </row>
     <row r="19" ht="13.5" customHeight="1">
       <c r="A19" t="s" s="6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -2224,7 +1606,7 @@
     </row>
     <row r="20" ht="13.5" customHeight="1">
       <c r="A20" t="s" s="6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
@@ -2233,7 +1615,7 @@
     </row>
     <row r="21" ht="13.5" customHeight="1">
       <c r="A21" t="s" s="6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
@@ -2242,7 +1624,7 @@
     </row>
     <row r="22" ht="13.5" customHeight="1">
       <c r="A22" t="s" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
@@ -2251,7 +1633,7 @@
     </row>
     <row r="23" ht="13.5" customHeight="1">
       <c r="A23" t="s" s="6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
@@ -2260,7 +1642,7 @@
     </row>
     <row r="24" ht="13.5" customHeight="1">
       <c r="A24" t="s" s="6">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
@@ -2269,7 +1651,7 @@
     </row>
     <row r="25" ht="13.5" customHeight="1">
       <c r="A25" t="s" s="6">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
@@ -2278,7 +1660,7 @@
     </row>
     <row r="26" ht="13.5" customHeight="1">
       <c r="A26" t="s" s="6">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
@@ -2287,7 +1669,7 @@
     </row>
     <row r="27" ht="13.5" customHeight="1">
       <c r="A27" t="s" s="6">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
@@ -2296,7 +1678,7 @@
     </row>
     <row r="28" ht="13.5" customHeight="1">
       <c r="A28" t="s" s="6">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
@@ -2305,7 +1687,7 @@
     </row>
     <row r="29" ht="13.5" customHeight="1">
       <c r="A29" t="s" s="6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
@@ -2314,7 +1696,7 @@
     </row>
     <row r="30" ht="13.5" customHeight="1">
       <c r="A30" t="s" s="6">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
@@ -2323,7 +1705,7 @@
     </row>
     <row r="31" ht="13.5" customHeight="1">
       <c r="A31" t="s" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
@@ -2332,7 +1714,7 @@
     </row>
     <row r="32" ht="13.5" customHeight="1">
       <c r="A32" t="s" s="6">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
@@ -2341,7 +1723,7 @@
     </row>
     <row r="33" ht="13.5" customHeight="1">
       <c r="A33" t="s" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
@@ -2350,7 +1732,7 @@
     </row>
     <row r="34" ht="13.5" customHeight="1">
       <c r="A34" t="s" s="6">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
@@ -2359,7 +1741,7 @@
     </row>
     <row r="35" ht="13.5" customHeight="1">
       <c r="A35" t="s" s="6">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2368,7 +1750,7 @@
     </row>
     <row r="36" ht="13.5" customHeight="1">
       <c r="A36" t="s" s="7">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
@@ -2377,7 +1759,7 @@
     </row>
     <row r="37" ht="13.5" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
@@ -2386,7 +1768,7 @@
     </row>
     <row r="38" ht="13.5" customHeight="1">
       <c r="A38" t="s" s="7">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
@@ -2395,7 +1777,7 @@
     </row>
     <row r="39" ht="13.5" customHeight="1">
       <c r="A39" t="s" s="7">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
@@ -2404,7 +1786,7 @@
     </row>
     <row r="40" ht="13.5" customHeight="1">
       <c r="A40" t="s" s="7">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="4"/>
@@ -2413,7 +1795,7 @@
     </row>
     <row r="41" ht="13.5" customHeight="1">
       <c r="A41" t="s" s="7">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
@@ -2422,7 +1804,7 @@
     </row>
     <row r="42" ht="13.5" customHeight="1">
       <c r="A42" t="s" s="7">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="4"/>
@@ -2431,7 +1813,7 @@
     </row>
     <row r="43" ht="13.5" customHeight="1">
       <c r="A43" t="s" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="4"/>
@@ -2440,7 +1822,7 @@
     </row>
     <row r="44" ht="13.5" customHeight="1">
       <c r="A44" t="s" s="7">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="4"/>
@@ -2449,7 +1831,7 @@
     </row>
     <row r="45" ht="13.5" customHeight="1">
       <c r="A45" t="s" s="7">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="4"/>
@@ -2458,7 +1840,7 @@
     </row>
     <row r="46" ht="13.5" customHeight="1">
       <c r="A46" t="s" s="7">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
@@ -2467,7 +1849,7 @@
     </row>
     <row r="47" ht="13.5" customHeight="1">
       <c r="A47" t="s" s="7">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
@@ -2476,7 +1858,7 @@
     </row>
     <row r="48" ht="13.5" customHeight="1">
       <c r="A48" t="s" s="7">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="4"/>
@@ -2485,7 +1867,7 @@
     </row>
     <row r="49" ht="13.5" customHeight="1">
       <c r="A49" t="s" s="7">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="4"/>
@@ -2494,7 +1876,7 @@
     </row>
     <row r="50" ht="13.5" customHeight="1">
       <c r="A50" t="s" s="7">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
@@ -2503,7 +1885,7 @@
     </row>
     <row r="51" ht="13.5" customHeight="1">
       <c r="A51" t="s" s="7">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="4"/>
@@ -2512,7 +1894,7 @@
     </row>
     <row r="52" ht="13.5" customHeight="1">
       <c r="A52" t="s" s="7">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="4"/>
@@ -2521,7 +1903,7 @@
     </row>
     <row r="53" ht="13.5" customHeight="1">
       <c r="A53" t="s" s="7">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="4"/>
@@ -2530,7 +1912,7 @@
     </row>
     <row r="54" ht="13.5" customHeight="1">
       <c r="A54" t="s" s="7">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
@@ -2539,7 +1921,7 @@
     </row>
     <row r="55" ht="13.5" customHeight="1">
       <c r="A55" t="s" s="7">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
@@ -2548,7 +1930,7 @@
     </row>
     <row r="56" ht="13.5" customHeight="1">
       <c r="A56" t="s" s="7">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="4"/>
@@ -2557,7 +1939,7 @@
     </row>
     <row r="57" ht="13.5" customHeight="1">
       <c r="A57" t="s" s="7">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="4"/>
@@ -2566,7 +1948,7 @@
     </row>
     <row r="58" ht="13.5" customHeight="1">
       <c r="A58" t="s" s="7">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
@@ -2575,7 +1957,7 @@
     </row>
     <row r="59" ht="13.5" customHeight="1">
       <c r="A59" t="s" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
@@ -2584,7 +1966,7 @@
     </row>
     <row r="60" ht="13.5" customHeight="1">
       <c r="A60" t="s" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
@@ -2593,7 +1975,7 @@
     </row>
     <row r="61" ht="13.5" customHeight="1">
       <c r="A61" t="s" s="7">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
@@ -2602,7 +1984,7 @@
     </row>
     <row r="62" ht="13.5" customHeight="1">
       <c r="A62" t="s" s="7">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
@@ -2611,7 +1993,7 @@
     </row>
     <row r="63" ht="13.5" customHeight="1">
       <c r="A63" t="s" s="7">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
@@ -2620,7 +2002,7 @@
     </row>
     <row r="64" ht="13.5" customHeight="1">
       <c r="A64" t="s" s="7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
@@ -2629,7 +2011,7 @@
     </row>
     <row r="65" ht="13.5" customHeight="1">
       <c r="A65" t="s" s="9">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="4"/>
@@ -2638,7 +2020,7 @@
     </row>
     <row r="66" ht="13.5" customHeight="1">
       <c r="A66" t="s" s="9">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
@@ -2647,7 +2029,7 @@
     </row>
     <row r="67" ht="13.5" customHeight="1">
       <c r="A67" t="s" s="9">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
@@ -2656,7 +2038,7 @@
     </row>
     <row r="68" ht="13.5" customHeight="1">
       <c r="A68" t="s" s="9">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
@@ -2665,7 +2047,7 @@
     </row>
     <row r="69" ht="13.5" customHeight="1">
       <c r="A69" t="s" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
@@ -2674,7 +2056,7 @@
     </row>
     <row r="70" ht="13.5" customHeight="1">
       <c r="A70" t="s" s="9">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
@@ -2683,7 +2065,7 @@
     </row>
     <row r="71" ht="13.5" customHeight="1">
       <c r="A71" t="s" s="9">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
@@ -2692,7 +2074,7 @@
     </row>
     <row r="72" ht="13.5" customHeight="1">
       <c r="A72" t="s" s="9">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
@@ -2701,7 +2083,7 @@
     </row>
     <row r="73" ht="13.5" customHeight="1">
       <c r="A73" t="s" s="9">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
@@ -2710,7 +2092,7 @@
     </row>
     <row r="74" ht="13.5" customHeight="1">
       <c r="A74" t="s" s="9">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
@@ -2719,7 +2101,7 @@
     </row>
     <row r="75" ht="13.5" customHeight="1">
       <c r="A75" t="s" s="9">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
@@ -2728,7 +2110,7 @@
     </row>
     <row r="76" ht="13.5" customHeight="1">
       <c r="A76" t="s" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
@@ -2737,7 +2119,7 @@
     </row>
     <row r="77" ht="13.5" customHeight="1">
       <c r="A77" t="s" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
@@ -2755,7 +2137,7 @@
     </row>
     <row r="79" ht="13.5" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="4"/>
@@ -2764,7 +2146,7 @@
     </row>
     <row r="80" ht="13.5" customHeight="1">
       <c r="A80" t="s" s="8">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
@@ -2773,7 +2155,7 @@
     </row>
     <row r="81" ht="13.5" customHeight="1">
       <c r="A81" t="s" s="8">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="4"/>
@@ -2782,7 +2164,7 @@
     </row>
     <row r="82" ht="13.5" customHeight="1">
       <c r="A82" t="s" s="9">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="4"/>
@@ -2791,7 +2173,7 @@
     </row>
     <row r="83" ht="13.5" customHeight="1">
       <c r="A83" t="s" s="9">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
@@ -2800,7 +2182,7 @@
     </row>
     <row r="84" ht="13.5" customHeight="1">
       <c r="A84" t="s" s="9">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
@@ -2809,7 +2191,7 @@
     </row>
     <row r="85" ht="13.5" customHeight="1">
       <c r="A85" t="s" s="9">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
@@ -2818,7 +2200,7 @@
     </row>
     <row r="86" ht="13.5" customHeight="1">
       <c r="A86" t="s" s="9">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
@@ -2827,7 +2209,7 @@
     </row>
     <row r="87" ht="13.5" customHeight="1">
       <c r="A87" t="s" s="9">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
@@ -2836,7 +2218,7 @@
     </row>
     <row r="88" ht="13.5" customHeight="1">
       <c r="A88" t="s" s="9">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="4"/>
@@ -2845,7 +2227,7 @@
     </row>
     <row r="89" ht="13.5" customHeight="1">
       <c r="A89" t="s" s="9">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
@@ -2854,7 +2236,7 @@
     </row>
     <row r="90" ht="13.5" customHeight="1">
       <c r="A90" t="s" s="9">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
@@ -2863,7 +2245,7 @@
     </row>
     <row r="91" ht="13.5" customHeight="1">
       <c r="A91" t="s" s="9">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="4"/>
@@ -2872,7 +2254,7 @@
     </row>
     <row r="92" ht="13.5" customHeight="1">
       <c r="A92" t="s" s="9">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="4"/>
@@ -2881,7 +2263,7 @@
     </row>
     <row r="93" ht="13.5" customHeight="1">
       <c r="A93" t="s" s="9">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="4"/>
@@ -2890,7 +2272,7 @@
     </row>
     <row r="94" ht="13.5" customHeight="1">
       <c r="A94" t="s" s="9">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="4"/>
@@ -2899,7 +2281,7 @@
     </row>
     <row r="95" ht="13.5" customHeight="1">
       <c r="A95" t="s" s="9">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="4"/>
@@ -2908,7 +2290,7 @@
     </row>
     <row r="96" ht="13.5" customHeight="1">
       <c r="A96" t="s" s="9">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="4"/>
@@ -2917,7 +2299,7 @@
     </row>
     <row r="97" ht="13.5" customHeight="1">
       <c r="A97" t="s" s="9">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="4"/>
@@ -2926,7 +2308,7 @@
     </row>
     <row r="98" ht="13.5" customHeight="1">
       <c r="A98" t="s" s="9">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="4"/>
@@ -2935,7 +2317,7 @@
     </row>
     <row r="99" ht="13.5" customHeight="1">
       <c r="A99" t="s" s="9">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="4"/>
@@ -2944,7 +2326,7 @@
     </row>
     <row r="100" ht="13.5" customHeight="1">
       <c r="A100" t="s" s="9">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="4"/>
@@ -2953,7 +2335,7 @@
     </row>
     <row r="101" ht="13.5" customHeight="1">
       <c r="A101" t="s" s="9">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="4"/>
@@ -2962,7 +2344,7 @@
     </row>
     <row r="102" ht="13.5" customHeight="1">
       <c r="A102" t="s" s="9">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -2971,7 +2353,7 @@
     </row>
     <row r="103" ht="13.5" customHeight="1">
       <c r="A103" t="s" s="9">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="4"/>
@@ -2980,7 +2362,7 @@
     </row>
     <row r="104" ht="13.5" customHeight="1">
       <c r="A104" t="s" s="9">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="4"/>
@@ -2989,7 +2371,7 @@
     </row>
     <row r="105" ht="13.5" customHeight="1">
       <c r="A105" t="s" s="9">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="4"/>
@@ -2998,7 +2380,7 @@
     </row>
     <row r="106" ht="13.5" customHeight="1">
       <c r="A106" t="s" s="8">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="4"/>
@@ -3007,7 +2389,7 @@
     </row>
     <row r="107" ht="13.5" customHeight="1">
       <c r="A107" t="s" s="8">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="4"/>
@@ -3015,2151 +2397,1673 @@
       <c r="E107" s="4"/>
     </row>
     <row r="108" ht="13.5" customHeight="1">
-      <c r="A108" t="s" s="8">
-        <v>84</v>
-      </c>
+      <c r="A108" s="8"/>
       <c r="B108" s="3"/>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
     </row>
     <row r="109" ht="13.5" customHeight="1">
-      <c r="A109" t="s" s="8">
-        <v>15</v>
-      </c>
+      <c r="A109" s="8"/>
       <c r="B109" s="3"/>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
     </row>
     <row r="110" ht="13.5" customHeight="1">
-      <c r="A110" t="s" s="8">
-        <v>85</v>
-      </c>
+      <c r="A110" s="8"/>
       <c r="B110" s="3"/>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
     </row>
     <row r="111" ht="13.5" customHeight="1">
-      <c r="A111" t="s" s="8">
-        <v>28</v>
-      </c>
+      <c r="A111" s="8"/>
       <c r="B111" s="3"/>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
     </row>
     <row r="112" ht="13.5" customHeight="1">
-      <c r="A112" t="s" s="8">
-        <v>86</v>
-      </c>
+      <c r="A112" s="8"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
     </row>
     <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" t="s" s="8">
-        <v>87</v>
-      </c>
+      <c r="A113" s="8"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
     </row>
     <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" t="s" s="8">
-        <v>87</v>
-      </c>
+      <c r="A114" s="8"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
     </row>
     <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" t="s" s="8">
-        <v>3</v>
-      </c>
+      <c r="A115" s="8"/>
       <c r="B115" s="3"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
     </row>
     <row r="116" ht="13.5" customHeight="1">
-      <c r="A116" t="s" s="8">
-        <v>88</v>
-      </c>
+      <c r="A116" s="8"/>
       <c r="B116" s="3"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
     </row>
     <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" t="s" s="8">
-        <v>89</v>
-      </c>
+      <c r="A117" s="8"/>
       <c r="B117" s="3"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
     </row>
     <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" t="s" s="8">
-        <v>90</v>
-      </c>
+      <c r="A118" s="8"/>
       <c r="B118" s="3"/>
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
     </row>
     <row r="119" ht="13.5" customHeight="1">
-      <c r="A119" t="s" s="8">
-        <v>91</v>
-      </c>
+      <c r="A119" s="8"/>
       <c r="B119" s="3"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
     </row>
     <row r="120" ht="13.5" customHeight="1">
-      <c r="A120" t="s" s="8">
-        <v>92</v>
-      </c>
+      <c r="A120" s="8"/>
       <c r="B120" s="3"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
     </row>
     <row r="121" ht="13.5" customHeight="1">
-      <c r="A121" t="s" s="8">
-        <v>93</v>
-      </c>
+      <c r="A121" s="8"/>
       <c r="B121" s="3"/>
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
     </row>
     <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" t="s" s="8">
-        <v>41</v>
-      </c>
+      <c r="A122" s="8"/>
       <c r="B122" s="3"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
     </row>
     <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" t="s" s="8">
-        <v>94</v>
-      </c>
+      <c r="A123" s="8"/>
       <c r="B123" s="3"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
     </row>
     <row r="124" ht="13.5" customHeight="1">
-      <c r="A124" t="s" s="8">
-        <v>95</v>
-      </c>
+      <c r="A124" s="8"/>
       <c r="B124" s="3"/>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
     </row>
     <row r="125" ht="13.5" customHeight="1">
-      <c r="A125" t="s" s="8">
-        <v>96</v>
-      </c>
+      <c r="A125" s="8"/>
       <c r="B125" s="3"/>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
     </row>
     <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" t="s" s="8">
-        <v>14</v>
-      </c>
+      <c r="A126" s="8"/>
       <c r="B126" s="3"/>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
     </row>
     <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" t="s" s="8">
-        <v>16</v>
-      </c>
+      <c r="A127" s="8"/>
       <c r="B127" s="3"/>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
     </row>
     <row r="128" ht="13.5" customHeight="1">
-      <c r="A128" t="s" s="8">
-        <v>46</v>
-      </c>
+      <c r="A128" s="8"/>
       <c r="B128" s="3"/>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
     </row>
     <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" t="s" s="8">
-        <v>97</v>
-      </c>
+      <c r="A129" s="8"/>
       <c r="B129" s="3"/>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
     </row>
     <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" t="s" s="8">
-        <v>98</v>
-      </c>
+      <c r="A130" s="8"/>
       <c r="B130" s="3"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
     </row>
     <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" t="s" s="8">
-        <v>99</v>
-      </c>
+      <c r="A131" s="8"/>
       <c r="B131" s="3"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
     </row>
     <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" t="s" s="8">
-        <v>100</v>
-      </c>
+      <c r="A132" s="8"/>
       <c r="B132" s="3"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
     </row>
     <row r="133" ht="13.5" customHeight="1">
-      <c r="A133" t="s" s="8">
-        <v>101</v>
-      </c>
+      <c r="A133" s="8"/>
       <c r="B133" s="3"/>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
     </row>
     <row r="134" ht="13.5" customHeight="1">
-      <c r="A134" t="s" s="8">
-        <v>102</v>
-      </c>
+      <c r="A134" s="8"/>
       <c r="B134" s="3"/>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
     </row>
     <row r="135" ht="13.5" customHeight="1">
-      <c r="A135" t="s" s="8">
-        <v>103</v>
-      </c>
+      <c r="A135" s="8"/>
       <c r="B135" s="3"/>
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
     </row>
     <row r="136" ht="13.5" customHeight="1">
-      <c r="A136" t="s" s="8">
-        <v>73</v>
-      </c>
+      <c r="A136" s="8"/>
       <c r="B136" s="3"/>
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
     </row>
     <row r="137" ht="13.5" customHeight="1">
-      <c r="A137" t="s" s="8">
-        <v>11</v>
-      </c>
+      <c r="A137" s="8"/>
       <c r="B137" s="3"/>
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
     </row>
     <row r="138" ht="13.5" customHeight="1">
-      <c r="A138" t="s" s="8">
-        <v>104</v>
-      </c>
+      <c r="A138" s="8"/>
       <c r="B138" s="3"/>
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
     </row>
     <row r="139" ht="13.5" customHeight="1">
-      <c r="A139" t="s" s="8">
-        <v>105</v>
-      </c>
+      <c r="A139" s="8"/>
       <c r="B139" s="3"/>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
     </row>
     <row r="140" ht="13.5" customHeight="1">
-      <c r="A140" t="s" s="8">
-        <v>106</v>
-      </c>
+      <c r="A140" s="8"/>
       <c r="B140" s="3"/>
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
     </row>
     <row r="141" ht="13.5" customHeight="1">
-      <c r="A141" t="s" s="8">
-        <v>107</v>
-      </c>
+      <c r="A141" s="8"/>
       <c r="B141" s="3"/>
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
     </row>
     <row r="142" ht="13.5" customHeight="1">
-      <c r="A142" t="s" s="8">
-        <v>108</v>
-      </c>
+      <c r="A142" s="8"/>
       <c r="B142" s="3"/>
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
     </row>
     <row r="143" ht="13.5" customHeight="1">
-      <c r="A143" t="s" s="8">
-        <v>109</v>
-      </c>
+      <c r="A143" s="8"/>
       <c r="B143" s="3"/>
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
     </row>
     <row r="144" ht="13.5" customHeight="1">
-      <c r="A144" t="s" s="8">
-        <v>110</v>
-      </c>
+      <c r="A144" s="8"/>
       <c r="B144" s="3"/>
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
     </row>
     <row r="145" ht="13.5" customHeight="1">
-      <c r="A145" t="s" s="8">
-        <v>30</v>
-      </c>
+      <c r="A145" s="8"/>
       <c r="B145" s="3"/>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
     </row>
     <row r="146" ht="13.5" customHeight="1">
-      <c r="A146" t="s" s="8">
-        <v>111</v>
-      </c>
+      <c r="A146" s="8"/>
       <c r="B146" s="3"/>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
     </row>
     <row r="147" ht="13.5" customHeight="1">
-      <c r="A147" t="s" s="8">
-        <v>36</v>
-      </c>
+      <c r="A147" s="8"/>
       <c r="B147" s="3"/>
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
     </row>
     <row r="148" ht="13.5" customHeight="1">
-      <c r="A148" t="s" s="8">
-        <v>112</v>
-      </c>
+      <c r="A148" s="8"/>
       <c r="B148" s="3"/>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
     </row>
     <row r="149" ht="13.5" customHeight="1">
-      <c r="A149" t="s" s="8">
-        <v>113</v>
-      </c>
+      <c r="A149" s="8"/>
       <c r="B149" s="3"/>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
     </row>
     <row r="150" ht="13.5" customHeight="1">
-      <c r="A150" t="s" s="8">
-        <v>64</v>
-      </c>
+      <c r="A150" s="8"/>
       <c r="B150" s="3"/>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
     </row>
     <row r="151" ht="13.5" customHeight="1">
-      <c r="A151" t="s" s="8">
-        <v>114</v>
-      </c>
+      <c r="A151" s="8"/>
       <c r="B151" s="3"/>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
     </row>
     <row r="152" ht="13.5" customHeight="1">
-      <c r="A152" t="s" s="8">
-        <v>115</v>
-      </c>
+      <c r="A152" s="8"/>
       <c r="B152" s="3"/>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
     </row>
     <row r="153" ht="13.5" customHeight="1">
-      <c r="A153" t="s" s="8">
-        <v>116</v>
-      </c>
+      <c r="A153" s="8"/>
       <c r="B153" s="3"/>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
     </row>
     <row r="154" ht="13.5" customHeight="1">
-      <c r="A154" t="s" s="8">
-        <v>117</v>
-      </c>
+      <c r="A154" s="8"/>
       <c r="B154" s="3"/>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
     </row>
     <row r="155" ht="13.5" customHeight="1">
-      <c r="A155" t="s" s="8">
-        <v>118</v>
-      </c>
+      <c r="A155" s="8"/>
       <c r="B155" s="3"/>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
     </row>
     <row r="156" ht="13.5" customHeight="1">
-      <c r="A156" t="s" s="8">
-        <v>46</v>
-      </c>
+      <c r="A156" s="8"/>
       <c r="B156" s="3"/>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
     </row>
     <row r="157" ht="13.5" customHeight="1">
-      <c r="A157" t="s" s="8">
-        <v>119</v>
-      </c>
+      <c r="A157" s="8"/>
       <c r="B157" s="3"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
     </row>
     <row r="158" ht="13.5" customHeight="1">
-      <c r="A158" t="s" s="8">
-        <v>120</v>
-      </c>
+      <c r="A158" s="8"/>
       <c r="B158" s="3"/>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
     </row>
     <row r="159" ht="13.5" customHeight="1">
-      <c r="A159" t="s" s="8">
-        <v>121</v>
-      </c>
+      <c r="A159" s="8"/>
       <c r="B159" s="3"/>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
     </row>
     <row r="160" ht="13.5" customHeight="1">
-      <c r="A160" t="s" s="8">
-        <v>122</v>
-      </c>
+      <c r="A160" s="8"/>
       <c r="B160" s="3"/>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
     </row>
     <row r="161" ht="13.5" customHeight="1">
-      <c r="A161" t="s" s="8">
-        <v>123</v>
-      </c>
+      <c r="A161" s="8"/>
       <c r="B161" s="3"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
     </row>
     <row r="162" ht="13.5" customHeight="1">
-      <c r="A162" t="s" s="8">
-        <v>123</v>
-      </c>
+      <c r="A162" s="8"/>
       <c r="B162" s="3"/>
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
     </row>
     <row r="163" ht="13.5" customHeight="1">
-      <c r="A163" t="s" s="8">
-        <v>21</v>
-      </c>
+      <c r="A163" s="8"/>
       <c r="B163" s="3"/>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
     </row>
     <row r="164" ht="13.5" customHeight="1">
-      <c r="A164" t="s" s="8">
-        <v>124</v>
-      </c>
+      <c r="A164" s="8"/>
       <c r="B164" s="3"/>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
     </row>
     <row r="165" ht="13.5" customHeight="1">
-      <c r="A165" t="s" s="8">
-        <v>29</v>
-      </c>
+      <c r="A165" s="8"/>
       <c r="B165" s="3"/>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
     </row>
     <row r="166" ht="13.5" customHeight="1">
-      <c r="A166" t="s" s="8">
-        <v>56</v>
-      </c>
+      <c r="A166" s="8"/>
       <c r="B166" s="3"/>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
     </row>
     <row r="167" ht="13.5" customHeight="1">
-      <c r="A167" t="s" s="8">
-        <v>34</v>
-      </c>
+      <c r="A167" s="8"/>
       <c r="B167" s="3"/>
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
     </row>
     <row r="168" ht="13.5" customHeight="1">
-      <c r="A168" t="s" s="8">
-        <v>125</v>
-      </c>
+      <c r="A168" s="8"/>
       <c r="B168" s="3"/>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
     </row>
     <row r="169" ht="13.5" customHeight="1">
-      <c r="A169" t="s" s="8">
-        <v>92</v>
-      </c>
+      <c r="A169" s="8"/>
       <c r="B169" s="3"/>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
     </row>
     <row r="170" ht="13.5" customHeight="1">
-      <c r="A170" t="s" s="8">
-        <v>126</v>
-      </c>
+      <c r="A170" s="8"/>
       <c r="B170" s="3"/>
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
     </row>
     <row r="171" ht="13.5" customHeight="1">
-      <c r="A171" t="s" s="8">
-        <v>39</v>
-      </c>
+      <c r="A171" s="8"/>
       <c r="B171" s="3"/>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
     </row>
     <row r="172" ht="13.5" customHeight="1">
-      <c r="A172" t="s" s="8">
-        <v>41</v>
-      </c>
+      <c r="A172" s="8"/>
       <c r="B172" s="3"/>
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
     </row>
     <row r="173" ht="13.5" customHeight="1">
-      <c r="A173" t="s" s="8">
-        <v>108</v>
-      </c>
+      <c r="A173" s="8"/>
       <c r="B173" s="3"/>
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
     </row>
     <row r="174" ht="13.5" customHeight="1">
-      <c r="A174" t="s" s="8">
-        <v>108</v>
-      </c>
+      <c r="A174" s="8"/>
       <c r="B174" s="3"/>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
     </row>
     <row r="175" ht="13.5" customHeight="1">
-      <c r="A175" t="s" s="8">
-        <v>127</v>
-      </c>
+      <c r="A175" s="8"/>
       <c r="B175" s="3"/>
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
     </row>
     <row r="176" ht="13.5" customHeight="1">
-      <c r="A176" t="s" s="8">
-        <v>128</v>
-      </c>
+      <c r="A176" s="8"/>
       <c r="B176" s="3"/>
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
     </row>
     <row r="177" ht="13.5" customHeight="1">
-      <c r="A177" t="s" s="8">
-        <v>129</v>
-      </c>
+      <c r="A177" s="8"/>
       <c r="B177" s="3"/>
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
     </row>
     <row r="178" ht="13.5" customHeight="1">
-      <c r="A178" t="s" s="8">
-        <v>130</v>
-      </c>
+      <c r="A178" s="8"/>
       <c r="B178" s="3"/>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
     </row>
     <row r="179" ht="13.5" customHeight="1">
-      <c r="A179" t="s" s="8">
-        <v>130</v>
-      </c>
+      <c r="A179" s="8"/>
       <c r="B179" s="3"/>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
     </row>
     <row r="180" ht="13.5" customHeight="1">
-      <c r="A180" t="s" s="8">
-        <v>131</v>
-      </c>
+      <c r="A180" s="8"/>
       <c r="B180" s="3"/>
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
     </row>
     <row r="181" ht="13.5" customHeight="1">
-      <c r="A181" t="s" s="8">
-        <v>33</v>
-      </c>
+      <c r="A181" s="8"/>
       <c r="B181" s="3"/>
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
     </row>
     <row r="182" ht="13.5" customHeight="1">
-      <c r="A182" t="s" s="8">
-        <v>132</v>
-      </c>
+      <c r="A182" s="8"/>
       <c r="B182" s="3"/>
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
     </row>
     <row r="183" ht="13.5" customHeight="1">
-      <c r="A183" t="s" s="8">
-        <v>133</v>
-      </c>
+      <c r="A183" s="8"/>
       <c r="B183" s="3"/>
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
     </row>
     <row r="184" ht="13.5" customHeight="1">
-      <c r="A184" t="s" s="8">
-        <v>134</v>
-      </c>
+      <c r="A184" s="8"/>
       <c r="B184" s="3"/>
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
     </row>
     <row r="185" ht="13.5" customHeight="1">
-      <c r="A185" t="s" s="8">
-        <v>135</v>
-      </c>
+      <c r="A185" s="8"/>
       <c r="B185" s="3"/>
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
     </row>
     <row r="186" ht="13.5" customHeight="1">
-      <c r="A186" t="s" s="8">
-        <v>136</v>
-      </c>
+      <c r="A186" s="8"/>
       <c r="B186" s="3"/>
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
     </row>
     <row r="187" ht="13.5" customHeight="1">
-      <c r="A187" t="s" s="8">
-        <v>137</v>
-      </c>
+      <c r="A187" s="8"/>
       <c r="B187" s="3"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
     </row>
     <row r="188" ht="13.5" customHeight="1">
-      <c r="A188" t="s" s="8">
-        <v>138</v>
-      </c>
+      <c r="A188" s="8"/>
       <c r="B188" s="3"/>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
     </row>
     <row r="189" ht="13.5" customHeight="1">
-      <c r="A189" t="s" s="8">
-        <v>139</v>
-      </c>
+      <c r="A189" s="8"/>
       <c r="B189" s="3"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
     </row>
     <row r="190" ht="13.5" customHeight="1">
-      <c r="A190" t="s" s="8">
-        <v>140</v>
-      </c>
+      <c r="A190" s="8"/>
       <c r="B190" s="3"/>
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
     </row>
     <row r="191" ht="13.5" customHeight="1">
-      <c r="A191" t="s" s="8">
-        <v>141</v>
-      </c>
+      <c r="A191" s="8"/>
       <c r="B191" s="3"/>
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
     </row>
     <row r="192" ht="13.5" customHeight="1">
-      <c r="A192" t="s" s="8">
-        <v>142</v>
-      </c>
+      <c r="A192" s="8"/>
       <c r="B192" s="3"/>
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
     </row>
     <row r="193" ht="13.5" customHeight="1">
-      <c r="A193" t="s" s="8">
-        <v>143</v>
-      </c>
+      <c r="A193" s="8"/>
       <c r="B193" s="3"/>
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
     </row>
     <row r="194" ht="13.5" customHeight="1">
-      <c r="A194" t="s" s="8">
-        <v>128</v>
-      </c>
+      <c r="A194" s="8"/>
       <c r="B194" s="3"/>
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
     </row>
     <row r="195" ht="13.5" customHeight="1">
-      <c r="A195" t="s" s="8">
-        <v>144</v>
-      </c>
+      <c r="A195" s="8"/>
       <c r="B195" s="3"/>
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
     </row>
     <row r="196" ht="13.5" customHeight="1">
-      <c r="A196" t="s" s="8">
-        <v>58</v>
-      </c>
+      <c r="A196" s="8"/>
       <c r="B196" s="3"/>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
     </row>
     <row r="197" ht="13.5" customHeight="1">
-      <c r="A197" t="s" s="8">
-        <v>58</v>
-      </c>
+      <c r="A197" s="8"/>
       <c r="B197" s="3"/>
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
     </row>
     <row r="198" ht="13.5" customHeight="1">
-      <c r="A198" t="s" s="8">
-        <v>59</v>
-      </c>
+      <c r="A198" s="8"/>
       <c r="B198" s="3"/>
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
     </row>
     <row r="199" ht="13.5" customHeight="1">
-      <c r="A199" t="s" s="8">
-        <v>145</v>
-      </c>
+      <c r="A199" s="8"/>
       <c r="B199" s="3"/>
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
     </row>
     <row r="200" ht="13.5" customHeight="1">
-      <c r="A200" t="s" s="8">
-        <v>146</v>
-      </c>
+      <c r="A200" s="8"/>
       <c r="B200" s="3"/>
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
     </row>
     <row r="201" ht="13.5" customHeight="1">
-      <c r="A201" t="s" s="8">
-        <v>147</v>
-      </c>
+      <c r="A201" s="8"/>
       <c r="B201" s="3"/>
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
     </row>
     <row r="202" ht="13.5" customHeight="1">
-      <c r="A202" t="s" s="8">
-        <v>148</v>
-      </c>
+      <c r="A202" s="8"/>
       <c r="B202" s="3"/>
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
     </row>
     <row r="203" ht="13.5" customHeight="1">
-      <c r="A203" t="s" s="8">
-        <v>148</v>
-      </c>
+      <c r="A203" s="8"/>
       <c r="B203" s="3"/>
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
     </row>
     <row r="204" ht="13.5" customHeight="1">
-      <c r="A204" t="s" s="8">
-        <v>37</v>
-      </c>
+      <c r="A204" s="8"/>
       <c r="B204" s="3"/>
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
     </row>
     <row r="205" ht="13.5" customHeight="1">
-      <c r="A205" t="s" s="8">
-        <v>149</v>
-      </c>
+      <c r="A205" s="8"/>
       <c r="B205" s="3"/>
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
     </row>
     <row r="206" ht="13.5" customHeight="1">
-      <c r="A206" t="s" s="8">
-        <v>150</v>
-      </c>
+      <c r="A206" s="8"/>
       <c r="B206" s="3"/>
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
     </row>
     <row r="207" ht="13.5" customHeight="1">
-      <c r="A207" t="s" s="8">
-        <v>15</v>
-      </c>
+      <c r="A207" s="8"/>
       <c r="B207" s="3"/>
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
     </row>
     <row r="208" ht="13.5" customHeight="1">
-      <c r="A208" t="s" s="8">
-        <v>16</v>
-      </c>
+      <c r="A208" s="8"/>
       <c r="B208" s="3"/>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
     </row>
     <row r="209" ht="13.5" customHeight="1">
-      <c r="A209" t="s" s="8">
-        <v>43</v>
-      </c>
+      <c r="A209" s="8"/>
       <c r="B209" s="3"/>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
     </row>
     <row r="210" ht="13.5" customHeight="1">
-      <c r="A210" t="s" s="8">
-        <v>19</v>
-      </c>
+      <c r="A210" s="8"/>
       <c r="B210" s="3"/>
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
     </row>
     <row r="211" ht="13.5" customHeight="1">
-      <c r="A211" t="s" s="8">
-        <v>151</v>
-      </c>
+      <c r="A211" s="8"/>
       <c r="B211" s="3"/>
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
     </row>
     <row r="212" ht="13.5" customHeight="1">
-      <c r="A212" t="s" s="8">
-        <v>152</v>
-      </c>
+      <c r="A212" s="8"/>
       <c r="B212" s="3"/>
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
     </row>
     <row r="213" ht="13.5" customHeight="1">
-      <c r="A213" t="s" s="8">
-        <v>66</v>
-      </c>
+      <c r="A213" s="8"/>
       <c r="B213" s="3"/>
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
     </row>
     <row r="214" ht="13.5" customHeight="1">
-      <c r="A214" t="s" s="8">
-        <v>153</v>
-      </c>
+      <c r="A214" s="8"/>
       <c r="B214" s="3"/>
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
     </row>
     <row r="215" ht="13.5" customHeight="1">
-      <c r="A215" t="s" s="8">
-        <v>51</v>
-      </c>
+      <c r="A215" s="8"/>
       <c r="B215" s="3"/>
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c r="A216" t="s" s="8">
-        <v>154</v>
-      </c>
+      <c r="A216" s="8"/>
       <c r="B216" s="3"/>
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
     </row>
     <row r="217" ht="13.5" customHeight="1">
-      <c r="A217" t="s" s="8">
-        <v>155</v>
-      </c>
+      <c r="A217" s="8"/>
       <c r="B217" s="3"/>
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
     </row>
     <row r="218" ht="13.5" customHeight="1">
-      <c r="A218" t="s" s="8">
-        <v>156</v>
-      </c>
+      <c r="A218" s="8"/>
       <c r="B218" s="3"/>
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
     </row>
     <row r="219" ht="13.5" customHeight="1">
-      <c r="A219" t="s" s="8">
-        <v>157</v>
-      </c>
+      <c r="A219" s="8"/>
       <c r="B219" s="3"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
     </row>
     <row r="220" ht="13.5" customHeight="1">
-      <c r="A220" t="s" s="8">
-        <v>158</v>
-      </c>
+      <c r="A220" s="8"/>
       <c r="B220" s="3"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
     </row>
     <row r="221" ht="13.5" customHeight="1">
-      <c r="A221" t="s" s="8">
-        <v>159</v>
-      </c>
+      <c r="A221" s="8"/>
       <c r="B221" s="3"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
     </row>
     <row r="222" ht="13.5" customHeight="1">
-      <c r="A222" t="s" s="8">
-        <v>160</v>
-      </c>
+      <c r="A222" s="8"/>
       <c r="B222" s="3"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
     </row>
     <row r="223" ht="13.5" customHeight="1">
-      <c r="A223" t="s" s="8">
-        <v>145</v>
-      </c>
+      <c r="A223" s="8"/>
       <c r="B223" s="3"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
     </row>
     <row r="224" ht="13.5" customHeight="1">
-      <c r="A224" t="s" s="8">
-        <v>36</v>
-      </c>
+      <c r="A224" s="8"/>
       <c r="B224" s="3"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
     </row>
     <row r="225" ht="13.5" customHeight="1">
-      <c r="A225" t="s" s="8">
-        <v>161</v>
-      </c>
+      <c r="A225" s="8"/>
       <c r="B225" s="3"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
     </row>
     <row r="226" ht="13.5" customHeight="1">
-      <c r="A226" t="s" s="8">
-        <v>150</v>
-      </c>
+      <c r="A226" s="8"/>
       <c r="B226" s="3"/>
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
     </row>
     <row r="227" ht="13.5" customHeight="1">
-      <c r="A227" t="s" s="8">
-        <v>96</v>
-      </c>
+      <c r="A227" s="8"/>
       <c r="B227" s="3"/>
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
     </row>
     <row r="228" ht="13.5" customHeight="1">
-      <c r="A228" t="s" s="8">
-        <v>117</v>
-      </c>
+      <c r="A228" s="8"/>
       <c r="B228" s="3"/>
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
     </row>
     <row r="229" ht="13.5" customHeight="1">
-      <c r="A229" t="s" s="8">
-        <v>1</v>
-      </c>
+      <c r="A229" s="8"/>
       <c r="B229" s="3"/>
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
     </row>
     <row r="230" ht="13.5" customHeight="1">
-      <c r="A230" t="s" s="8">
-        <v>1</v>
-      </c>
+      <c r="A230" s="8"/>
       <c r="B230" s="3"/>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
     </row>
     <row r="231" ht="13.5" customHeight="1">
-      <c r="A231" t="s" s="8">
-        <v>108</v>
-      </c>
+      <c r="A231" s="8"/>
       <c r="B231" s="3"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
     </row>
     <row r="232" ht="13.5" customHeight="1">
-      <c r="A232" t="s" s="8">
-        <v>162</v>
-      </c>
+      <c r="A232" s="8"/>
       <c r="B232" s="3"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
     </row>
     <row r="233" ht="13.5" customHeight="1">
-      <c r="A233" t="s" s="8">
-        <v>163</v>
-      </c>
+      <c r="A233" s="8"/>
       <c r="B233" s="3"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
     </row>
     <row r="234" ht="13.5" customHeight="1">
-      <c r="A234" t="s" s="8">
-        <v>164</v>
-      </c>
+      <c r="A234" s="8"/>
       <c r="B234" s="3"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
     </row>
     <row r="235" ht="13.5" customHeight="1">
-      <c r="A235" t="s" s="8">
-        <v>165</v>
-      </c>
+      <c r="A235" s="8"/>
       <c r="B235" s="3"/>
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
     </row>
     <row r="236" ht="13.5" customHeight="1">
-      <c r="A236" t="s" s="8">
-        <v>166</v>
-      </c>
+      <c r="A236" s="8"/>
       <c r="B236" s="3"/>
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
     </row>
     <row r="237" ht="13.5" customHeight="1">
-      <c r="A237" t="s" s="8">
-        <v>167</v>
-      </c>
+      <c r="A237" s="8"/>
       <c r="B237" s="3"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
     </row>
     <row r="238" ht="13.5" customHeight="1">
-      <c r="A238" t="s" s="8">
-        <v>168</v>
-      </c>
+      <c r="A238" s="8"/>
       <c r="B238" s="3"/>
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
     </row>
     <row r="239" ht="13.5" customHeight="1">
-      <c r="A239" t="s" s="8">
-        <v>56</v>
-      </c>
+      <c r="A239" s="8"/>
       <c r="B239" s="3"/>
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
     </row>
     <row r="240" ht="13.5" customHeight="1">
-      <c r="A240" t="s" s="8">
-        <v>169</v>
-      </c>
+      <c r="A240" s="8"/>
       <c r="B240" s="3"/>
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
     </row>
     <row r="241" ht="13.5" customHeight="1">
-      <c r="A241" t="s" s="8">
-        <v>61</v>
-      </c>
+      <c r="A241" s="8"/>
       <c r="B241" s="3"/>
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
     </row>
     <row r="242" ht="13.5" customHeight="1">
-      <c r="A242" t="s" s="8">
-        <v>170</v>
-      </c>
+      <c r="A242" s="8"/>
       <c r="B242" s="3"/>
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
     </row>
     <row r="243" ht="13.5" customHeight="1">
-      <c r="A243" t="s" s="8">
-        <v>171</v>
-      </c>
+      <c r="A243" s="8"/>
       <c r="B243" s="3"/>
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
     </row>
     <row r="244" ht="13.5" customHeight="1">
-      <c r="A244" t="s" s="8">
-        <v>172</v>
-      </c>
+      <c r="A244" s="8"/>
       <c r="B244" s="3"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
     </row>
     <row r="245" ht="13.5" customHeight="1">
-      <c r="A245" t="s" s="8">
-        <v>36</v>
-      </c>
+      <c r="A245" s="8"/>
       <c r="B245" s="3"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
     </row>
     <row r="246" ht="13.5" customHeight="1">
-      <c r="A246" t="s" s="8">
-        <v>173</v>
-      </c>
+      <c r="A246" s="8"/>
       <c r="B246" s="3"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
     </row>
     <row r="247" ht="13.5" customHeight="1">
-      <c r="A247" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A247" s="8"/>
       <c r="B247" s="3"/>
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
     </row>
     <row r="248" ht="13.5" customHeight="1">
-      <c r="A248" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A248" s="8"/>
       <c r="B248" s="3"/>
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
     </row>
     <row r="249" ht="13.5" customHeight="1">
-      <c r="A249" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A249" s="8"/>
       <c r="B249" s="3"/>
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
     </row>
     <row r="250" ht="13.5" customHeight="1">
-      <c r="A250" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A250" s="8"/>
       <c r="B250" s="3"/>
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
     </row>
     <row r="251" ht="13.5" customHeight="1">
-      <c r="A251" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A251" s="8"/>
       <c r="B251" s="3"/>
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
     </row>
     <row r="252" ht="13.5" customHeight="1">
-      <c r="A252" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A252" s="8"/>
       <c r="B252" s="3"/>
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
     </row>
     <row r="253" ht="13.5" customHeight="1">
-      <c r="A253" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A253" s="8"/>
       <c r="B253" s="3"/>
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
     </row>
     <row r="254" ht="13.5" customHeight="1">
-      <c r="A254" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A254" s="8"/>
       <c r="B254" s="3"/>
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
     </row>
     <row r="255" ht="13.5" customHeight="1">
-      <c r="A255" t="s" s="8">
-        <v>174</v>
-      </c>
+      <c r="A255" s="8"/>
       <c r="B255" s="3"/>
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
     </row>
     <row r="256" ht="13.5" customHeight="1">
-      <c r="A256" t="s" s="8">
-        <v>175</v>
-      </c>
+      <c r="A256" s="8"/>
       <c r="B256" s="3"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
     </row>
     <row r="257" ht="13.5" customHeight="1">
-      <c r="A257" t="s" s="8">
-        <v>176</v>
-      </c>
+      <c r="A257" s="8"/>
       <c r="B257" s="3"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
     </row>
     <row r="258" ht="13.5" customHeight="1">
-      <c r="A258" t="s" s="8">
-        <v>176</v>
-      </c>
+      <c r="A258" s="8"/>
       <c r="B258" s="3"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
     </row>
     <row r="259" ht="13.5" customHeight="1">
-      <c r="A259" t="s" s="8">
-        <v>16</v>
-      </c>
+      <c r="A259" s="8"/>
       <c r="B259" s="3"/>
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
     </row>
     <row r="260" ht="13.5" customHeight="1">
-      <c r="A260" t="s" s="8">
-        <v>177</v>
-      </c>
+      <c r="A260" s="8"/>
       <c r="B260" s="3"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
     </row>
     <row r="261" ht="13.5" customHeight="1">
-      <c r="A261" t="s" s="8">
-        <v>178</v>
-      </c>
+      <c r="A261" s="8"/>
       <c r="B261" s="3"/>
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
     </row>
     <row r="262" ht="13.5" customHeight="1">
-      <c r="A262" t="s" s="8">
-        <v>2</v>
-      </c>
+      <c r="A262" s="8"/>
       <c r="B262" s="3"/>
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
     </row>
     <row r="263" ht="13.5" customHeight="1">
-      <c r="A263" t="s" s="8">
-        <v>179</v>
-      </c>
+      <c r="A263" s="8"/>
       <c r="B263" s="3"/>
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
     </row>
     <row r="264" ht="13.5" customHeight="1">
-      <c r="A264" t="s" s="8">
-        <v>108</v>
-      </c>
+      <c r="A264" s="8"/>
       <c r="B264" s="3"/>
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
     </row>
     <row r="265" ht="13.5" customHeight="1">
-      <c r="A265" t="s" s="8">
-        <v>180</v>
-      </c>
+      <c r="A265" s="8"/>
       <c r="B265" s="3"/>
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
     </row>
     <row r="266" ht="13.5" customHeight="1">
-      <c r="A266" t="s" s="8">
-        <v>181</v>
-      </c>
+      <c r="A266" s="8"/>
       <c r="B266" s="3"/>
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
     </row>
     <row r="267" ht="13.5" customHeight="1">
-      <c r="A267" t="s" s="8">
-        <v>163</v>
-      </c>
+      <c r="A267" s="8"/>
       <c r="B267" s="3"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
     </row>
     <row r="268" ht="13.5" customHeight="1">
-      <c r="A268" t="s" s="8">
-        <v>87</v>
-      </c>
+      <c r="A268" s="8"/>
       <c r="B268" s="3"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
     </row>
     <row r="269" ht="13.5" customHeight="1">
-      <c r="A269" t="s" s="8">
-        <v>182</v>
-      </c>
+      <c r="A269" s="8"/>
       <c r="B269" s="3"/>
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
     </row>
     <row r="270" ht="13.5" customHeight="1">
-      <c r="A270" t="s" s="8">
-        <v>165</v>
-      </c>
+      <c r="A270" s="8"/>
       <c r="B270" s="3"/>
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
     </row>
     <row r="271" ht="13.5" customHeight="1">
-      <c r="A271" t="s" s="8">
-        <v>183</v>
-      </c>
+      <c r="A271" s="8"/>
       <c r="B271" s="3"/>
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
     </row>
     <row r="272" ht="13.5" customHeight="1">
-      <c r="A272" t="s" s="8">
-        <v>184</v>
-      </c>
+      <c r="A272" s="8"/>
       <c r="B272" s="3"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
     </row>
     <row r="273" ht="13.5" customHeight="1">
-      <c r="A273" t="s" s="8">
-        <v>185</v>
-      </c>
+      <c r="A273" s="8"/>
       <c r="B273" s="3"/>
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
     </row>
     <row r="274" ht="13.5" customHeight="1">
-      <c r="A274" t="s" s="8">
-        <v>186</v>
-      </c>
+      <c r="A274" s="8"/>
       <c r="B274" s="3"/>
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
     </row>
     <row r="275" ht="13.5" customHeight="1">
-      <c r="A275" t="s" s="8">
-        <v>187</v>
-      </c>
+      <c r="A275" s="8"/>
       <c r="B275" s="3"/>
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
     </row>
     <row r="276" ht="13.5" customHeight="1">
-      <c r="A276" t="s" s="8">
-        <v>156</v>
-      </c>
+      <c r="A276" s="8"/>
       <c r="B276" s="3"/>
       <c r="C276" s="4"/>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
     </row>
     <row r="277" ht="13.5" customHeight="1">
-      <c r="A277" t="s" s="8">
-        <v>188</v>
-      </c>
+      <c r="A277" s="8"/>
       <c r="B277" s="3"/>
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
     </row>
     <row r="278" ht="13.5" customHeight="1">
-      <c r="A278" t="s" s="8">
-        <v>189</v>
-      </c>
+      <c r="A278" s="8"/>
       <c r="B278" s="3"/>
       <c r="C278" s="4"/>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
     </row>
     <row r="279" ht="13.5" customHeight="1">
-      <c r="A279" t="s" s="8">
-        <v>190</v>
-      </c>
+      <c r="A279" s="8"/>
       <c r="B279" s="3"/>
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
     </row>
     <row r="280" ht="13.5" customHeight="1">
-      <c r="A280" t="s" s="8">
-        <v>54</v>
-      </c>
+      <c r="A280" s="8"/>
       <c r="B280" s="3"/>
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
     </row>
     <row r="281" ht="13.5" customHeight="1">
-      <c r="A281" t="s" s="8">
-        <v>191</v>
-      </c>
+      <c r="A281" s="8"/>
       <c r="B281" s="3"/>
       <c r="C281" s="4"/>
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
     </row>
     <row r="282" ht="13.5" customHeight="1">
-      <c r="A282" t="s" s="8">
-        <v>192</v>
-      </c>
+      <c r="A282" s="8"/>
       <c r="B282" s="3"/>
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
     </row>
     <row r="283" ht="13.5" customHeight="1">
-      <c r="A283" t="s" s="8">
-        <v>193</v>
-      </c>
+      <c r="A283" s="8"/>
       <c r="B283" s="3"/>
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
     </row>
     <row r="284" ht="13.5" customHeight="1">
-      <c r="A284" t="s" s="8">
-        <v>194</v>
-      </c>
+      <c r="A284" s="8"/>
       <c r="B284" s="3"/>
       <c r="C284" s="4"/>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
     </row>
     <row r="285" ht="13.5" customHeight="1">
-      <c r="A285" t="s" s="8">
-        <v>194</v>
-      </c>
+      <c r="A285" s="8"/>
       <c r="B285" s="3"/>
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
     </row>
     <row r="286" ht="13.5" customHeight="1">
-      <c r="A286" t="s" s="8">
-        <v>56</v>
-      </c>
+      <c r="A286" s="8"/>
       <c r="B286" s="3"/>
       <c r="C286" s="4"/>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
     </row>
     <row r="287" ht="13.5" customHeight="1">
-      <c r="A287" t="s" s="8">
-        <v>195</v>
-      </c>
+      <c r="A287" s="8"/>
       <c r="B287" s="3"/>
       <c r="C287" s="4"/>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
     </row>
     <row r="288" ht="13.5" customHeight="1">
-      <c r="A288" t="s" s="8">
-        <v>196</v>
-      </c>
+      <c r="A288" s="8"/>
       <c r="B288" s="3"/>
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
     </row>
     <row r="289" ht="13.5" customHeight="1">
-      <c r="A289" t="s" s="8">
-        <v>197</v>
-      </c>
+      <c r="A289" s="8"/>
       <c r="B289" s="3"/>
       <c r="C289" s="4"/>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
     </row>
     <row r="290" ht="13.5" customHeight="1">
-      <c r="A290" t="s" s="8">
-        <v>198</v>
-      </c>
+      <c r="A290" s="8"/>
       <c r="B290" s="3"/>
       <c r="C290" s="4"/>
       <c r="D290" s="4"/>
       <c r="E290" s="4"/>
     </row>
     <row r="291" ht="13.5" customHeight="1">
-      <c r="A291" t="s" s="8">
-        <v>199</v>
-      </c>
+      <c r="A291" s="8"/>
       <c r="B291" s="3"/>
       <c r="C291" s="4"/>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
     </row>
     <row r="292" ht="13.5" customHeight="1">
-      <c r="A292" t="s" s="8">
-        <v>200</v>
-      </c>
+      <c r="A292" s="8"/>
       <c r="B292" s="3"/>
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
     </row>
     <row r="293" ht="13.5" customHeight="1">
-      <c r="A293" t="s" s="8">
-        <v>201</v>
-      </c>
+      <c r="A293" s="8"/>
       <c r="B293" s="3"/>
       <c r="C293" s="4"/>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
     </row>
     <row r="294" ht="13.5" customHeight="1">
-      <c r="A294" t="s" s="8">
-        <v>201</v>
-      </c>
+      <c r="A294" s="8"/>
       <c r="B294" s="3"/>
       <c r="C294" s="4"/>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
     </row>
     <row r="295" ht="13.5" customHeight="1">
-      <c r="A295" t="s" s="8">
-        <v>202</v>
-      </c>
+      <c r="A295" s="8"/>
       <c r="B295" s="3"/>
       <c r="C295" s="4"/>
       <c r="D295" s="4"/>
       <c r="E295" s="4"/>
     </row>
     <row r="296" ht="13.5" customHeight="1">
-      <c r="A296" t="s" s="8">
-        <v>203</v>
-      </c>
+      <c r="A296" s="8"/>
       <c r="B296" s="3"/>
       <c r="C296" s="4"/>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
     </row>
     <row r="297" ht="13.5" customHeight="1">
-      <c r="A297" t="s" s="8">
-        <v>204</v>
-      </c>
+      <c r="A297" s="8"/>
       <c r="B297" s="3"/>
       <c r="C297" s="4"/>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
     </row>
     <row r="298" ht="13.5" customHeight="1">
-      <c r="A298" t="s" s="8">
-        <v>205</v>
-      </c>
+      <c r="A298" s="8"/>
       <c r="B298" s="3"/>
       <c r="C298" s="4"/>
       <c r="D298" s="4"/>
       <c r="E298" s="4"/>
     </row>
     <row r="299" ht="13.5" customHeight="1">
-      <c r="A299" t="s" s="8">
-        <v>206</v>
-      </c>
+      <c r="A299" s="8"/>
       <c r="B299" s="3"/>
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
     </row>
     <row r="300" ht="13.5" customHeight="1">
-      <c r="A300" t="s" s="8">
-        <v>207</v>
-      </c>
+      <c r="A300" s="8"/>
       <c r="B300" s="3"/>
       <c r="C300" s="4"/>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
     </row>
     <row r="301" ht="13.5" customHeight="1">
-      <c r="A301" t="s" s="8">
-        <v>208</v>
-      </c>
+      <c r="A301" s="8"/>
       <c r="B301" s="3"/>
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
     </row>
     <row r="302" ht="13.5" customHeight="1">
-      <c r="A302" t="s" s="8">
-        <v>209</v>
-      </c>
+      <c r="A302" s="8"/>
       <c r="B302" s="3"/>
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
       <c r="E302" s="4"/>
     </row>
     <row r="303" ht="13.5" customHeight="1">
-      <c r="A303" t="s" s="8">
-        <v>210</v>
-      </c>
+      <c r="A303" s="8"/>
       <c r="B303" s="3"/>
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
       <c r="E303" s="4"/>
     </row>
     <row r="304" ht="13.5" customHeight="1">
-      <c r="A304" t="s" s="8">
-        <v>160</v>
-      </c>
+      <c r="A304" s="8"/>
       <c r="B304" s="3"/>
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
       <c r="E304" s="4"/>
     </row>
     <row r="305" ht="13.5" customHeight="1">
-      <c r="A305" t="s" s="8">
-        <v>211</v>
-      </c>
+      <c r="A305" s="8"/>
       <c r="B305" s="3"/>
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
       <c r="E305" s="4"/>
     </row>
     <row r="306" ht="13.5" customHeight="1">
-      <c r="A306" t="s" s="8">
-        <v>211</v>
-      </c>
+      <c r="A306" s="8"/>
       <c r="B306" s="3"/>
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
       <c r="E306" s="4"/>
     </row>
     <row r="307" ht="13.5" customHeight="1">
-      <c r="A307" t="s" s="8">
-        <v>212</v>
-      </c>
+      <c r="A307" s="8"/>
       <c r="B307" s="3"/>
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
     </row>
     <row r="308" ht="13.5" customHeight="1">
-      <c r="A308" t="s" s="8">
-        <v>172</v>
-      </c>
+      <c r="A308" s="8"/>
       <c r="B308" s="3"/>
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
     </row>
     <row r="309" ht="13.5" customHeight="1">
-      <c r="A309" t="s" s="8">
-        <v>172</v>
-      </c>
+      <c r="A309" s="8"/>
       <c r="B309" s="3"/>
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
     </row>
     <row r="310" ht="13.5" customHeight="1">
-      <c r="A310" t="s" s="8">
-        <v>81</v>
-      </c>
+      <c r="A310" s="8"/>
       <c r="B310" s="3"/>
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
       <c r="E310" s="4"/>
     </row>
     <row r="311" ht="13.5" customHeight="1">
-      <c r="A311" t="s" s="8">
-        <v>150</v>
-      </c>
+      <c r="A311" s="8"/>
       <c r="B311" s="3"/>
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
     </row>
     <row r="312" ht="13.5" customHeight="1">
-      <c r="A312" t="s" s="8">
-        <v>117</v>
-      </c>
+      <c r="A312" s="8"/>
       <c r="B312" s="3"/>
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
       <c r="E312" s="4"/>
     </row>
     <row r="313" ht="13.5" customHeight="1">
-      <c r="A313" t="s" s="8">
-        <v>213</v>
-      </c>
+      <c r="A313" s="8"/>
       <c r="B313" s="3"/>
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
     </row>
     <row r="314" ht="13.5" customHeight="1">
-      <c r="A314" t="s" s="8">
-        <v>214</v>
-      </c>
+      <c r="A314" s="8"/>
       <c r="B314" s="3"/>
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
       <c r="E314" s="4"/>
     </row>
     <row r="315" ht="13.5" customHeight="1">
-      <c r="A315" t="s" s="8">
-        <v>215</v>
-      </c>
+      <c r="A315" s="8"/>
       <c r="B315" s="3"/>
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
     </row>
     <row r="316" ht="13.5" customHeight="1">
-      <c r="A316" t="s" s="8">
-        <v>179</v>
-      </c>
+      <c r="A316" s="8"/>
       <c r="B316" s="3"/>
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
       <c r="E316" s="4"/>
     </row>
     <row r="317" ht="13.5" customHeight="1">
-      <c r="A317" t="s" s="8">
-        <v>216</v>
-      </c>
+      <c r="A317" s="8"/>
       <c r="B317" s="3"/>
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
     </row>
     <row r="318" ht="13.5" customHeight="1">
-      <c r="A318" t="s" s="8">
-        <v>216</v>
-      </c>
+      <c r="A318" s="8"/>
       <c r="B318" s="3"/>
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
     </row>
     <row r="319" ht="13.5" customHeight="1">
-      <c r="A319" t="s" s="8">
-        <v>217</v>
-      </c>
+      <c r="A319" s="8"/>
       <c r="B319" s="3"/>
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
     </row>
     <row r="320" ht="13.5" customHeight="1">
-      <c r="A320" t="s" s="8">
-        <v>218</v>
-      </c>
+      <c r="A320" s="8"/>
       <c r="B320" s="3"/>
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
     </row>
     <row r="321" ht="13.5" customHeight="1">
-      <c r="A321" t="s" s="8">
-        <v>219</v>
-      </c>
+      <c r="A321" s="8"/>
       <c r="B321" s="3"/>
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
     </row>
     <row r="322" ht="13.5" customHeight="1">
-      <c r="A322" t="s" s="8">
-        <v>54</v>
-      </c>
+      <c r="A322" s="8"/>
       <c r="B322" s="3"/>
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
     </row>
     <row r="323" ht="13.5" customHeight="1">
-      <c r="A323" t="s" s="8">
-        <v>29</v>
-      </c>
+      <c r="A323" s="8"/>
       <c r="B323" s="3"/>
       <c r="C323" s="4"/>
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
     </row>
     <row r="324" ht="13.5" customHeight="1">
-      <c r="A324" t="s" s="8">
-        <v>56</v>
-      </c>
+      <c r="A324" s="8"/>
       <c r="B324" s="3"/>
       <c r="C324" s="4"/>
       <c r="D324" s="4"/>
       <c r="E324" s="4"/>
     </row>
     <row r="325" ht="13.5" customHeight="1">
-      <c r="A325" t="s" s="8">
-        <v>220</v>
-      </c>
+      <c r="A325" s="8"/>
       <c r="B325" s="3"/>
       <c r="C325" s="4"/>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
     </row>
     <row r="326" ht="13.5" customHeight="1">
-      <c r="A326" t="s" s="8">
-        <v>221</v>
-      </c>
+      <c r="A326" s="8"/>
       <c r="B326" s="3"/>
       <c r="C326" s="4"/>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
     </row>
     <row r="327" ht="13.5" customHeight="1">
-      <c r="A327" t="s" s="8">
-        <v>222</v>
-      </c>
+      <c r="A327" s="8"/>
       <c r="B327" s="3"/>
       <c r="C327" s="4"/>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
     </row>
     <row r="328" ht="13.5" customHeight="1">
-      <c r="A328" t="s" s="8">
-        <v>173</v>
-      </c>
+      <c r="A328" s="8"/>
       <c r="B328" s="3"/>
       <c r="C328" s="4"/>
       <c r="D328" s="4"/>
       <c r="E328" s="4"/>
     </row>
     <row r="329" ht="13.5" customHeight="1">
-      <c r="A329" t="s" s="8">
-        <v>223</v>
-      </c>
+      <c r="A329" s="8"/>
       <c r="B329" s="3"/>
       <c r="C329" s="4"/>
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
     </row>
     <row r="330" ht="13.5" customHeight="1">
-      <c r="A330" t="s" s="8">
-        <v>41</v>
-      </c>
+      <c r="A330" s="8"/>
       <c r="B330" s="3"/>
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
     </row>
     <row r="331" ht="13.5" customHeight="1">
-      <c r="A331" t="s" s="8">
-        <v>224</v>
-      </c>
+      <c r="A331" s="8"/>
       <c r="B331" s="3"/>
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
     </row>
     <row r="332" ht="13.5" customHeight="1">
-      <c r="A332" t="s" s="8">
-        <v>225</v>
-      </c>
+      <c r="A332" s="8"/>
       <c r="B332" s="3"/>
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
     </row>
     <row r="333" ht="13.5" customHeight="1">
-      <c r="A333" t="s" s="8">
-        <v>214</v>
-      </c>
+      <c r="A333" s="8"/>
       <c r="B333" s="3"/>
       <c r="C333" s="4"/>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
     </row>
     <row r="334" ht="13.5" customHeight="1">
-      <c r="A334" t="s" s="8">
-        <v>43</v>
-      </c>
+      <c r="A334" s="8"/>
       <c r="B334" s="3"/>
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
     </row>
     <row r="335" ht="13.5" customHeight="1">
-      <c r="A335" t="s" s="8">
-        <v>19</v>
-      </c>
+      <c r="A335" s="8"/>
       <c r="B335" s="3"/>
       <c r="C335" s="4"/>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
     </row>
     <row r="336" ht="13.5" customHeight="1">
-      <c r="A336" t="s" s="8">
-        <v>154</v>
-      </c>
+      <c r="A336" s="8"/>
       <c r="B336" s="3"/>
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
     </row>
     <row r="337" ht="13.5" customHeight="1">
-      <c r="A337" t="s" s="8">
-        <v>226</v>
-      </c>
+      <c r="A337" s="8"/>
       <c r="B337" s="3"/>
       <c r="C337" s="4"/>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
     </row>
     <row r="338" ht="13.5" customHeight="1">
-      <c r="A338" t="s" s="8">
-        <v>137</v>
-      </c>
+      <c r="A338" s="8"/>
       <c r="B338" s="3"/>
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
     </row>
     <row r="339" ht="13.5" customHeight="1">
-      <c r="A339" t="s" s="8">
-        <v>155</v>
-      </c>
+      <c r="A339" s="8"/>
       <c r="B339" s="3"/>
       <c r="C339" s="4"/>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
     </row>
     <row r="340" ht="13.5" customHeight="1">
-      <c r="A340" t="s" s="8">
-        <v>67</v>
-      </c>
+      <c r="A340" s="8"/>
       <c r="B340" s="3"/>
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
     </row>
     <row r="341" ht="13.5" customHeight="1">
-      <c r="A341" t="s" s="8">
-        <v>21</v>
-      </c>
+      <c r="A341" s="8"/>
       <c r="B341" s="3"/>
       <c r="C341" s="4"/>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
     </row>
     <row r="342" ht="13.5" customHeight="1">
-      <c r="A342" t="s" s="8">
-        <v>12</v>
-      </c>
+      <c r="A342" s="8"/>
       <c r="B342" s="3"/>
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
     </row>
     <row r="343" ht="13.5" customHeight="1">
-      <c r="A343" t="s" s="8">
-        <v>227</v>
-      </c>
+      <c r="A343" s="8"/>
       <c r="B343" s="3"/>
       <c r="C343" s="4"/>
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
     </row>
     <row r="344" ht="13.5" customHeight="1">
-      <c r="A344" t="s" s="8">
-        <v>228</v>
-      </c>
+      <c r="A344" s="8"/>
       <c r="B344" s="3"/>
       <c r="C344" s="4"/>
       <c r="D344" s="4"/>
       <c r="E344" s="4"/>
     </row>
     <row r="345" ht="13.5" customHeight="1">
-      <c r="A345" t="s" s="8">
-        <v>222</v>
-      </c>
+      <c r="A345" s="8"/>
       <c r="B345" s="3"/>
       <c r="C345" s="4"/>
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
     </row>
     <row r="346" ht="13.5" customHeight="1">
-      <c r="A346" t="s" s="8">
-        <v>63</v>
-      </c>
+      <c r="A346" s="8"/>
       <c r="B346" s="3"/>
       <c r="C346" s="4"/>
       <c r="D346" s="4"/>
